--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.5381,0.3505,0.2072,0.0189</t>
-  </si>
-  <si>
-    <t>0.6273,0.1764,0.2770,0.0197</t>
-  </si>
-  <si>
-    <t>0.4128,0.5247,0.1214,0.0127</t>
-  </si>
-  <si>
-    <t>0.5411,0.3112,0.2180,0.0196</t>
-  </si>
-  <si>
-    <t>0.4640,0.5423,0.0879,0.0201</t>
-  </si>
-  <si>
-    <t>0.4164,0.5924,0.0789,0.0199</t>
-  </si>
-  <si>
-    <t>0.4117,0.5825,0.0930,0.0128</t>
-  </si>
-  <si>
-    <t>0.3601,0.5820,0.1461,0.0234</t>
-  </si>
-  <si>
-    <t>0.6187,0.3782,0.0884,0.0189</t>
-  </si>
-  <si>
-    <t>0.3190,0.6865,0.0815,0.0214</t>
-  </si>
-  <si>
-    <t>0.4990,0.4986,0.1154,0.0269</t>
-  </si>
-  <si>
-    <t>0.4280,0.4953,0.1734,0.0146</t>
-  </si>
-  <si>
-    <t>0.5605,0.2460,0.1840,0.0046</t>
-  </si>
-  <si>
-    <t>0.6077,0.1431,0.2955,0.0062</t>
-  </si>
-  <si>
-    <t>0.5013,0.1970,0.3353,0.0070</t>
-  </si>
-  <si>
-    <t>0.5528,0.0964,0.4561,0.0098</t>
-  </si>
-  <si>
-    <t>0.4646,0.3516,0.2227,0.0101</t>
-  </si>
-  <si>
-    <t>0.3737,0.5625,0.0960,0.0058</t>
-  </si>
-  <si>
-    <t>0.5187,0.4113,0.1446,0.0121</t>
-  </si>
-  <si>
-    <t>0.2034,0.7416,0.1152,0.0110</t>
-  </si>
-  <si>
-    <t>0.1795,0.7835,0.0945,0.0077</t>
-  </si>
-  <si>
-    <t>0.3326,0.5763,0.1278,0.0084</t>
-  </si>
-  <si>
-    <t>0.6625,0.0694,0.3377,0.0042</t>
-  </si>
-  <si>
-    <t>0.5205,0.1291,0.3861,0.0075</t>
-  </si>
-  <si>
-    <t>0.4671,0.0446,0.6330,0.0073</t>
-  </si>
-  <si>
-    <t>0.6328,0.0804,0.3572,0.0056</t>
-  </si>
-  <si>
-    <t>0.1846,0.0419,0.8687,0.0019</t>
-  </si>
-  <si>
-    <t>0.3814,0.0862,0.6578,0.0097</t>
-  </si>
-  <si>
-    <t>0.2202,0.0348,0.8360,0.0027</t>
-  </si>
-  <si>
-    <t>0.4517,0.4345,0.1616,0.0091</t>
-  </si>
-  <si>
-    <t>0.5354,0.3590,0.2058,0.0185</t>
-  </si>
-  <si>
-    <t>0.0498,0.2875,0.8687,0.0035</t>
-  </si>
-  <si>
-    <t>0.3378,0.3981,0.1695,0.0018</t>
-  </si>
-  <si>
-    <t>0.5005,0.4419,0.1274,0.0127</t>
-  </si>
-  <si>
-    <t>0.3480,0.5838,0.1756,0.0267</t>
-  </si>
-  <si>
-    <t>0.2904,0.6577,0.1341,0.0146</t>
-  </si>
-  <si>
-    <t>0.4734,0.4486,0.1489,0.0095</t>
-  </si>
-  <si>
-    <t>0.2804,0.1758,0.5377,0.0033</t>
-  </si>
-  <si>
-    <t>0.5506,0.0564,0.5011,0.0046</t>
-  </si>
-  <si>
-    <t>0.4896,0.0591,0.5685,0.0033</t>
-  </si>
-  <si>
-    <t>0.6058,0.1011,0.3484,0.0048</t>
-  </si>
-  <si>
-    <t>0.6032,0.0418,0.5095,0.0028</t>
-  </si>
-  <si>
-    <t>0.2986,0.2620,0.3045,0.0022</t>
-  </si>
-  <si>
-    <t>0.6281,0.0463,0.4475,0.0038</t>
-  </si>
-  <si>
-    <t>0.3993,0.4502,0.2743,0.0243</t>
-  </si>
-  <si>
-    <t>0.1719,0.7851,0.0723,0.0062</t>
-  </si>
-  <si>
-    <t>0.4639,0.3422,0.1403,0.0036</t>
-  </si>
-  <si>
-    <t>0.4342,0.3830,0.1934,0.0051</t>
-  </si>
-  <si>
-    <t>0.2468,0.0531,0.8026,0.0029</t>
-  </si>
-  <si>
-    <t>0.1072,0.1009,0.8687,0.0027</t>
-  </si>
-  <si>
-    <t>0.5101,0.0629,0.5347,0.0063</t>
-  </si>
-  <si>
-    <t>0.5857,0.0459,0.5096,0.0049</t>
-  </si>
-  <si>
-    <t>0.0305,0.1168,0.9411,0.0018</t>
-  </si>
-  <si>
-    <t>0.2994,0.1342,0.5698,0.0038</t>
-  </si>
-  <si>
-    <t>0.5333,0.4206,0.1306,0.0198</t>
-  </si>
-  <si>
-    <t>0.5036,0.4636,0.1296,0.0179</t>
-  </si>
-  <si>
-    <t>0.4791,0.5410,0.1002,0.0276</t>
-  </si>
-  <si>
-    <t>0.3825,0.4254,0.2427,0.0116</t>
-  </si>
-  <si>
-    <t>0.4714,0.5261,0.0841,0.0136</t>
-  </si>
-  <si>
-    <t>0.3589,0.6058,0.1335,0.0286</t>
-  </si>
-  <si>
-    <t>0.6630,0.3094,0.1168,0.0286</t>
-  </si>
-  <si>
-    <t>0.0251,0.9043,0.3701,0.0032</t>
-  </si>
-  <si>
-    <t>0.0871,0.1449,0.8686,0.0028</t>
-  </si>
-  <si>
-    <t>0.2362,0.1421,0.6360,0.0025</t>
-  </si>
-  <si>
-    <t>0.2243,0.2242,0.5154,0.0023</t>
-  </si>
-  <si>
-    <t>0.1213,0.0823,0.8885,0.0016</t>
-  </si>
-  <si>
-    <t>0.1960,0.7402,0.0807,0.0063</t>
-  </si>
-  <si>
-    <t>0.0113,0.9823,0.0144,0.0008</t>
-  </si>
-  <si>
-    <t>0.3673,0.4780,0.1978,0.0115</t>
-  </si>
-  <si>
-    <t>0.3641,0.4945,0.2405,0.0144</t>
-  </si>
-  <si>
-    <t>0.0219,0.2737,0.9475,0.0020</t>
-  </si>
-  <si>
-    <t>0.2626,0.4107,0.2581,0.0024</t>
-  </si>
-  <si>
-    <t>0.2867,0.2448,0.4989,0.0034</t>
-  </si>
-  <si>
-    <t>0.0680,0.8625,0.1203,0.0020</t>
-  </si>
-  <si>
-    <t>0.1075,0.5261,0.4551,0.0015</t>
-  </si>
-  <si>
-    <t>0.6015,0.1442,0.3539,0.0137</t>
-  </si>
-  <si>
-    <t>0.5260,0.4103,0.1960,0.0296</t>
-  </si>
-  <si>
-    <t>0.5774,0.2965,0.2125,0.0277</t>
-  </si>
-  <si>
-    <t>0.6286,0.2603,0.1773,0.0228</t>
-  </si>
-  <si>
-    <t>0.5841,0.2678,0.2385,0.0267</t>
-  </si>
-  <si>
-    <t>0.6332,0.2106,0.2712,0.0285</t>
-  </si>
-  <si>
-    <t>0.1255,0.3178,0.6339,0.0018</t>
-  </si>
-  <si>
-    <t>0.1579,0.1088,0.8145,0.0024</t>
-  </si>
-  <si>
-    <t>0.2136,0.2844,0.3624,0.0021</t>
-  </si>
-  <si>
-    <t>0.4306,0.0618,0.6274,0.0060</t>
-  </si>
-  <si>
-    <t>0.2247,0.3124,0.4800,0.0021</t>
-  </si>
-  <si>
-    <t>0.4228,0.2682,0.2593,0.0032</t>
-  </si>
-  <si>
-    <t>0.4225,0.5407,0.1153,0.0160</t>
-  </si>
-  <si>
-    <t>0.4281,0.5576,0.0979,0.0151</t>
-  </si>
-  <si>
-    <t>0.3812,0.6006,0.1156,0.0222</t>
-  </si>
-  <si>
-    <t>0.5064,0.4566,0.1158,0.0149</t>
-  </si>
-  <si>
-    <t>0.4503,0.5502,0.1071,0.0212</t>
-  </si>
-  <si>
-    <t>0.4588,0.5536,0.0791,0.0112</t>
-  </si>
-  <si>
-    <t>0.3792,0.5941,0.1130,0.0202</t>
-  </si>
-  <si>
-    <t>0.3315,0.5892,0.1398,0.0105</t>
-  </si>
-  <si>
-    <t>0.4666,0.5056,0.1180,0.0131</t>
-  </si>
-  <si>
-    <t>0.3087,0.5946,0.1975,0.0115</t>
-  </si>
-  <si>
-    <t>0.5630,0.4508,0.0745,0.0179</t>
-  </si>
-  <si>
-    <t>0.6118,0.3796,0.0815,0.0329</t>
-  </si>
-  <si>
-    <t>0.5621,0.4387,0.0976,0.0181</t>
-  </si>
-  <si>
-    <t>0.2988,0.7110,0.0676,0.0146</t>
-  </si>
-  <si>
-    <t>0.4109,0.5482,0.1363,0.0227</t>
-  </si>
-  <si>
-    <t>0.4231,0.5675,0.0969,0.0212</t>
-  </si>
-  <si>
-    <t>0.0058,0.0870,0.9885,0.0005</t>
-  </si>
-  <si>
-    <t>0.6167,0.0537,0.4512,0.0103</t>
-  </si>
-  <si>
-    <t>0.6006,0.1597,0.2477,0.0059</t>
-  </si>
-  <si>
-    <t>0.4767,0.0927,0.4566,0.0050</t>
-  </si>
-  <si>
-    <t>0.1350,0.8394,0.0697,0.0076</t>
-  </si>
-  <si>
-    <t>0.4550,0.5016,0.1332,0.0167</t>
-  </si>
-  <si>
-    <t>0.3944,0.5369,0.1213,0.0062</t>
-  </si>
-  <si>
-    <t>0.4165,0.5418,0.1150,0.0111</t>
-  </si>
-  <si>
-    <t>0.4242,0.5037,0.1714,0.0199</t>
-  </si>
-  <si>
-    <t>0.1921,0.7819,0.0714,0.0084</t>
-  </si>
-  <si>
-    <t>0.2926,0.6510,0.1299,0.0152</t>
-  </si>
-  <si>
-    <t>0.3964,0.3702,0.2668,0.0109</t>
-  </si>
-  <si>
-    <t>0.5766,0.0582,0.5048,0.0069</t>
-  </si>
-  <si>
-    <t>0.5892,0.1889,0.2489,0.0072</t>
-  </si>
-  <si>
-    <t>0.5609,0.2264,0.2119,0.0068</t>
-  </si>
-  <si>
-    <t>0.6143,0.2563,0.2132,0.0190</t>
-  </si>
-  <si>
-    <t>0.4695,0.3512,0.1979,0.0061</t>
-  </si>
-  <si>
-    <t>0.3902,0.5282,0.1090,0.0050</t>
-  </si>
-  <si>
-    <t>0.2885,0.5834,0.1502,0.0074</t>
-  </si>
-  <si>
-    <t>0.1058,0.8368,0.0660,0.0017</t>
-  </si>
-  <si>
-    <t>0.2953,0.5947,0.1937,0.0150</t>
-  </si>
-  <si>
-    <t>0.3945,0.6034,0.0840,0.0139</t>
-  </si>
-  <si>
-    <t>0.3106,0.6321,0.1129,0.0126</t>
-  </si>
-  <si>
-    <t>0.2913,0.6896,0.1045,0.0112</t>
-  </si>
-  <si>
-    <t>0.5557,0.3901,0.1342,0.0186</t>
-  </si>
-  <si>
-    <t>0.3225,0.6475,0.1093,0.0162</t>
-  </si>
-  <si>
-    <t>0.4320,0.5395,0.1013,0.0142</t>
-  </si>
-  <si>
-    <t>0.4641,0.4831,0.1288,0.0174</t>
-  </si>
-  <si>
-    <t>0.4370,0.4536,0.1938,0.0126</t>
-  </si>
-  <si>
-    <t>0.5197,0.4441,0.1216,0.0170</t>
-  </si>
-  <si>
-    <t>0.3780,0.5952,0.1274,0.0232</t>
-  </si>
-  <si>
-    <t>0.4157,0.0704,0.6459,0.0041</t>
-  </si>
-  <si>
-    <t>0.3626,0.1015,0.5663,0.0022</t>
-  </si>
-  <si>
-    <t>0.1560,0.0568,0.8647,0.0019</t>
-  </si>
-  <si>
-    <t>0.5407,0.1027,0.3917,0.0028</t>
-  </si>
-  <si>
-    <t>0.5248,0.1861,0.3719,0.0083</t>
-  </si>
-  <si>
-    <t>0.6833,0.1415,0.2137,0.0074</t>
-  </si>
-  <si>
-    <t>0.5585,0.1477,0.3464,0.0080</t>
-  </si>
-  <si>
-    <t>0.6348,0.2262,0.1621,0.0101</t>
-  </si>
-  <si>
-    <t>0.5792,0.3239,0.1613,0.0267</t>
-  </si>
-  <si>
-    <t>0.5757,0.0717,0.4648,0.0263</t>
-  </si>
-  <si>
-    <t>0.6822,0.1475,0.2304,0.0150</t>
-  </si>
-  <si>
-    <t>0.6163,0.2178,0.2690,0.0321</t>
-  </si>
-  <si>
-    <t>0.1791,0.4994,0.3614,0.0050</t>
-  </si>
-  <si>
-    <t>0.4149,0.4661,0.2291,0.0192</t>
-  </si>
-  <si>
-    <t>0.4904,0.4562,0.1553,0.0197</t>
-  </si>
-  <si>
-    <t>0.5400,0.4147,0.1400,0.0218</t>
-  </si>
-  <si>
-    <t>0.2844,0.6616,0.1379,0.0206</t>
-  </si>
-  <si>
-    <t>0.5502,0.4226,0.1176,0.0178</t>
-  </si>
-  <si>
-    <t>0.5446,0.3789,0.1678,0.0276</t>
-  </si>
-  <si>
-    <t>0.4650,0.5029,0.1349,0.0165</t>
-  </si>
-  <si>
-    <t>0.1035,0.3838,0.7261,0.0108</t>
-  </si>
-  <si>
-    <t>0.5868,0.3350,0.1572,0.0273</t>
-  </si>
-  <si>
-    <t>0.2502,0.6626,0.1802,0.0204</t>
-  </si>
-  <si>
-    <t>0.4178,0.4371,0.1695,0.0097</t>
-  </si>
-  <si>
-    <t>0.4528,0.4775,0.1507,0.0191</t>
-  </si>
-  <si>
-    <t>0.4204,0.4777,0.2057,0.0186</t>
-  </si>
-  <si>
-    <t>0.5067,0.4162,0.1117,0.0063</t>
-  </si>
-  <si>
-    <t>0.7151,0.2098,0.1274,0.0089</t>
-  </si>
-  <si>
-    <t>0.2959,0.6343,0.1651,0.0183</t>
-  </si>
-  <si>
-    <t>0.3867,0.6092,0.0830,0.0152</t>
-  </si>
-  <si>
-    <t>0.4642,0.5529,0.0867,0.0280</t>
-  </si>
-  <si>
-    <t>0.3349,0.6286,0.1424,0.0219</t>
-  </si>
-  <si>
-    <t>0.4950,0.5057,0.0925,0.0189</t>
-  </si>
-  <si>
-    <t>0.3800,0.5720,0.1369,0.0193</t>
-  </si>
-  <si>
-    <t>0.4060,0.5663,0.1052,0.0179</t>
-  </si>
-  <si>
-    <t>0.5273,0.4259,0.1446,0.0128</t>
-  </si>
-  <si>
-    <t>0.3650,0.5974,0.1109,0.0147</t>
-  </si>
-  <si>
-    <t>0.4315,0.5767,0.1000,0.0183</t>
-  </si>
-  <si>
-    <t>0.3298,0.6390,0.1446,0.0243</t>
-  </si>
-  <si>
-    <t>0.3439,0.6208,0.1112,0.0158</t>
-  </si>
-  <si>
-    <t>0.3421,0.5839,0.1569,0.0199</t>
-  </si>
-  <si>
-    <t>0.3300,0.6266,0.1221,0.0175</t>
-  </si>
-  <si>
-    <t>0.6565,0.2978,0.1284,0.0247</t>
-  </si>
-  <si>
-    <t>0.6370,0.3479,0.0813,0.0164</t>
-  </si>
-  <si>
-    <t>0.3594,0.5914,0.1378,0.0170</t>
-  </si>
-  <si>
-    <t>0.0824,0.4375,0.6906,0.0033</t>
-  </si>
-  <si>
-    <t>0.5447,0.4435,0.0996,0.0114</t>
-  </si>
-  <si>
-    <t>0.3099,0.0354,0.7501,0.0047</t>
-  </si>
-  <si>
-    <t>0.4575,0.0428,0.6474,0.0045</t>
-  </si>
-  <si>
-    <t>0.5589,0.0731,0.4706,0.0063</t>
-  </si>
-  <si>
-    <t>0.2848,0.1878,0.5600,0.0074</t>
-  </si>
-  <si>
-    <t>0.4130,0.0635,0.6378,0.0056</t>
-  </si>
-  <si>
-    <t>0.1248,0.1161,0.8211,0.0017</t>
-  </si>
-  <si>
-    <t>0.4743,0.0441,0.6202,0.0030</t>
-  </si>
-  <si>
-    <t>0.4110,0.3399,0.2668,0.0086</t>
-  </si>
-  <si>
-    <t>0.5627,0.0941,0.4041,0.0068</t>
-  </si>
-  <si>
-    <t>0.5820,0.1904,0.2732,0.0069</t>
-  </si>
-  <si>
-    <t>0.4824,0.3102,0.2268,0.0091</t>
-  </si>
-  <si>
-    <t>0.6676,0.1242,0.2406,0.0063</t>
-  </si>
-  <si>
-    <t>0.6644,0.2203,0.1423,0.0075</t>
-  </si>
-  <si>
-    <t>0.4823,0.3196,0.1979,0.0080</t>
-  </si>
-  <si>
-    <t>0.6426,0.1166,0.2278,0.0043</t>
-  </si>
-  <si>
-    <t>0.3321,0.6577,0.0829,0.0098</t>
-  </si>
-  <si>
-    <t>0.4472,0.5476,0.0979,0.0151</t>
-  </si>
-  <si>
-    <t>0.3563,0.6166,0.1321,0.0194</t>
-  </si>
-  <si>
-    <t>0.4602,0.5244,0.1073,0.0156</t>
-  </si>
-  <si>
-    <t>0.3772,0.5270,0.1834,0.0153</t>
-  </si>
-  <si>
-    <t>0.5185,0.2794,0.1831,0.0077</t>
-  </si>
-  <si>
-    <t>0.6682,0.1024,0.2815,0.0048</t>
-  </si>
-  <si>
-    <t>0.6327,0.2084,0.1775,0.0104</t>
-  </si>
-  <si>
-    <t>0.4313,0.1601,0.4455,0.0068</t>
-  </si>
-  <si>
-    <t>0.6095,0.1471,0.3173,0.0115</t>
-  </si>
-  <si>
-    <t>0.6869,0.0911,0.3088,0.0044</t>
-  </si>
-  <si>
-    <t>0.5323,0.0818,0.4666,0.0051</t>
-  </si>
-  <si>
-    <t>0.6246,0.0218,0.5228,0.0030</t>
-  </si>
-  <si>
-    <t>0.4195,0.1309,0.4698,0.0026</t>
-  </si>
-  <si>
-    <t>0.6437,0.0290,0.5034,0.0021</t>
-  </si>
-  <si>
-    <t>0.4397,0.5153,0.1227,0.0119</t>
-  </si>
-  <si>
-    <t>0.3517,0.6315,0.1247,0.0234</t>
-  </si>
-  <si>
-    <t>0.4152,0.5172,0.1471,0.0118</t>
-  </si>
-  <si>
-    <t>0.4395,0.5245,0.1315,0.0201</t>
-  </si>
-  <si>
-    <t>0.3579,0.5935,0.1214,0.0182</t>
-  </si>
-  <si>
-    <t>0.4125,0.5602,0.1079,0.0169</t>
-  </si>
-  <si>
-    <t>0.5605,0.4264,0.1083,0.0165</t>
-  </si>
-  <si>
-    <t>0.2656,0.6872,0.1390,0.0298</t>
-  </si>
-  <si>
-    <t>0.6892,0.1622,0.2065,0.0122</t>
-  </si>
-  <si>
-    <t>0.4421,0.3562,0.2611,0.0155</t>
-  </si>
-  <si>
-    <t>0.3966,0.5503,0.0820,0.0054</t>
-  </si>
-  <si>
-    <t>0.1564,0.0541,0.8670,0.0023</t>
-  </si>
-  <si>
-    <t>0.2744,0.0391,0.7782,0.0027</t>
-  </si>
-  <si>
-    <t>0.6604,0.0556,0.4127,0.0032</t>
-  </si>
-  <si>
-    <t>0.0567,0.0783,0.9233,0.0015</t>
-  </si>
-  <si>
-    <t>0.5419,0.1729,0.3017,0.0056</t>
-  </si>
-  <si>
-    <t>0.1089,0.0748,0.8827,0.0029</t>
-  </si>
-  <si>
-    <t>0.3653,0.0524,0.7207,0.0036</t>
-  </si>
-  <si>
-    <t>0.5932,0.2225,0.2072,0.0077</t>
-  </si>
-  <si>
-    <t>0.7955,0.0585,0.1847,0.0048</t>
-  </si>
-  <si>
-    <t>0.7174,0.0756,0.2522,0.0038</t>
-  </si>
-  <si>
-    <t>0.6976,0.0787,0.3026,0.0092</t>
-  </si>
-  <si>
-    <t>0.6088,0.3942,0.0831,0.0176</t>
-  </si>
-  <si>
-    <t>0.4851,0.5092,0.1033,0.0234</t>
-  </si>
-  <si>
-    <t>0.5271,0.4688,0.1114,0.0178</t>
-  </si>
-  <si>
-    <t>0.3473,0.6192,0.1141,0.0119</t>
-  </si>
-  <si>
-    <t>0.4433,0.5567,0.0984,0.0283</t>
-  </si>
-  <si>
-    <t>0.5469,0.4760,0.0564,0.0178</t>
-  </si>
-  <si>
-    <t>0.2750,0.6720,0.1507,0.0145</t>
-  </si>
-  <si>
-    <t>0.5234,0.4878,0.0944,0.0173</t>
-  </si>
-  <si>
-    <t>0.4988,0.0416,0.5821,0.0033</t>
-  </si>
-  <si>
-    <t>0.1381,0.2145,0.6875,0.0016</t>
-  </si>
-  <si>
-    <t>0.1389,0.0874,0.8384,0.0026</t>
-  </si>
-  <si>
-    <t>0.1232,0.1874,0.7545,0.0036</t>
-  </si>
-  <si>
-    <t>0.2472,0.0558,0.7818,0.0026</t>
-  </si>
-  <si>
-    <t>0.7236,0.0468,0.3177,0.0031</t>
-  </si>
-  <si>
-    <t>0.5732,0.1610,0.2725,0.0048</t>
-  </si>
-  <si>
-    <t>0.5882,0.0350,0.5222,0.0033</t>
-  </si>
-  <si>
-    <t>0.5418,0.2391,0.2977,0.0150</t>
-  </si>
-  <si>
-    <t>0.6366,0.2000,0.2168,0.0180</t>
-  </si>
-  <si>
-    <t>0.3914,0.4595,0.2569,0.0478</t>
-  </si>
-  <si>
-    <t>0.7395,0.1146,0.2080,0.0236</t>
-  </si>
-  <si>
-    <t>0.6387,0.2172,0.1979,0.0217</t>
-  </si>
-  <si>
-    <t>0.4350,0.4554,0.1623,0.0143</t>
+    <t>0.6050,0.1683,0.2573,0.0075</t>
+  </si>
+  <si>
+    <t>0.7056,0.1709,0.1807,0.0145</t>
+  </si>
+  <si>
+    <t>0.4350,0.4705,0.1902,0.0262</t>
+  </si>
+  <si>
+    <t>0.4676,0.3890,0.1822,0.0109</t>
+  </si>
+  <si>
+    <t>0.6521,0.3109,0.0948,0.0356</t>
+  </si>
+  <si>
+    <t>0.4911,0.4932,0.1003,0.0223</t>
+  </si>
+  <si>
+    <t>0.2694,0.7001,0.0855,0.0118</t>
+  </si>
+  <si>
+    <t>0.3052,0.6547,0.1264,0.0187</t>
+  </si>
+  <si>
+    <t>0.3037,0.6765,0.1051,0.0141</t>
+  </si>
+  <si>
+    <t>0.3651,0.6255,0.1218,0.0266</t>
+  </si>
+  <si>
+    <t>0.4681,0.5579,0.0772,0.0239</t>
+  </si>
+  <si>
+    <t>0.4416,0.5760,0.0859,0.0211</t>
+  </si>
+  <si>
+    <t>0.6146,0.1121,0.3403,0.0062</t>
+  </si>
+  <si>
+    <t>0.4709,0.1553,0.4223,0.0075</t>
+  </si>
+  <si>
+    <t>0.6547,0.0865,0.3461,0.0081</t>
+  </si>
+  <si>
+    <t>0.5880,0.1698,0.2669,0.0055</t>
+  </si>
+  <si>
+    <t>0.4528,0.2881,0.2605,0.0071</t>
+  </si>
+  <si>
+    <t>0.4525,0.4836,0.1403,0.0119</t>
+  </si>
+  <si>
+    <t>0.3602,0.5535,0.1448,0.0094</t>
+  </si>
+  <si>
+    <t>0.4261,0.4488,0.2105,0.0147</t>
+  </si>
+  <si>
+    <t>0.1769,0.8006,0.0797,0.0072</t>
+  </si>
+  <si>
+    <t>0.3076,0.6439,0.0868,0.0071</t>
+  </si>
+  <si>
+    <t>0.5615,0.1388,0.3724,0.0090</t>
+  </si>
+  <si>
+    <t>0.7002,0.0332,0.3908,0.0046</t>
+  </si>
+  <si>
+    <t>0.3997,0.0504,0.6587,0.0060</t>
+  </si>
+  <si>
+    <t>0.6400,0.0663,0.3817,0.0043</t>
+  </si>
+  <si>
+    <t>0.3649,0.1639,0.5231,0.0057</t>
+  </si>
+  <si>
+    <t>0.5424,0.1157,0.4175,0.0070</t>
+  </si>
+  <si>
+    <t>0.1127,0.0387,0.9165,0.0021</t>
+  </si>
+  <si>
+    <t>0.3748,0.4726,0.1543,0.0044</t>
+  </si>
+  <si>
+    <t>0.2334,0.5684,0.2434,0.0100</t>
+  </si>
+  <si>
+    <t>0.0359,0.4796,0.8638,0.0071</t>
+  </si>
+  <si>
+    <t>0.3226,0.4866,0.1629,0.0049</t>
+  </si>
+  <si>
+    <t>0.5269,0.4025,0.1618,0.0294</t>
+  </si>
+  <si>
+    <t>0.3595,0.5679,0.1703,0.0244</t>
+  </si>
+  <si>
+    <t>0.6085,0.3889,0.0563,0.0057</t>
+  </si>
+  <si>
+    <t>0.4433,0.5020,0.1289,0.0105</t>
+  </si>
+  <si>
+    <t>0.2621,0.1010,0.7007,0.0034</t>
+  </si>
+  <si>
+    <t>0.6126,0.0338,0.5281,0.0049</t>
+  </si>
+  <si>
+    <t>0.6868,0.0414,0.4014,0.0016</t>
+  </si>
+  <si>
+    <t>0.5650,0.0213,0.6016,0.0034</t>
+  </si>
+  <si>
+    <t>0.5222,0.0979,0.3986,0.0035</t>
+  </si>
+  <si>
+    <t>0.0638,0.9117,0.0383,0.0008</t>
+  </si>
+  <si>
+    <t>0.5008,0.0500,0.5599,0.0037</t>
+  </si>
+  <si>
+    <t>0.4357,0.4920,0.1603,0.0131</t>
+  </si>
+  <si>
+    <t>0.2029,0.7069,0.1136,0.0044</t>
+  </si>
+  <si>
+    <t>0.4042,0.3997,0.2185,0.0069</t>
+  </si>
+  <si>
+    <t>0.3176,0.5491,0.1406,0.0058</t>
+  </si>
+  <si>
+    <t>0.0566,0.2949,0.8685,0.0048</t>
+  </si>
+  <si>
+    <t>0.1759,0.0482,0.8411,0.0016</t>
+  </si>
+  <si>
+    <t>0.4681,0.1946,0.3250,0.0042</t>
+  </si>
+  <si>
+    <t>0.5563,0.1148,0.3949,0.0060</t>
+  </si>
+  <si>
+    <t>0.1235,0.0836,0.8382,0.0021</t>
+  </si>
+  <si>
+    <t>0.4813,0.0562,0.5738,0.0036</t>
+  </si>
+  <si>
+    <t>0.3157,0.6349,0.1240,0.0146</t>
+  </si>
+  <si>
+    <t>0.4639,0.5078,0.1092,0.0188</t>
+  </si>
+  <si>
+    <t>0.4306,0.5671,0.0821,0.0180</t>
+  </si>
+  <si>
+    <t>0.0587,0.8632,0.1591,0.0063</t>
+  </si>
+  <si>
+    <t>0.4539,0.4677,0.1741,0.0211</t>
+  </si>
+  <si>
+    <t>0.3514,0.6530,0.0723,0.0152</t>
+  </si>
+  <si>
+    <t>0.3689,0.5950,0.1336,0.0142</t>
+  </si>
+  <si>
+    <t>0.2532,0.2671,0.5223,0.0031</t>
+  </si>
+  <si>
+    <t>0.3410,0.0775,0.6749,0.0049</t>
+  </si>
+  <si>
+    <t>0.0721,0.2839,0.7697,0.0021</t>
+  </si>
+  <si>
+    <t>0.1807,0.3692,0.4669,0.0030</t>
+  </si>
+  <si>
+    <t>0.3044,0.0326,0.7832,0.0026</t>
+  </si>
+  <si>
+    <t>0.3380,0.5910,0.0886,0.0052</t>
+  </si>
+  <si>
+    <t>0.0340,0.9578,0.0163,0.0016</t>
+  </si>
+  <si>
+    <t>0.4212,0.3429,0.2296,0.0042</t>
+  </si>
+  <si>
+    <t>0.2950,0.5830,0.2024,0.0137</t>
+  </si>
+  <si>
+    <t>0.1214,0.6807,0.2625,0.0036</t>
+  </si>
+  <si>
+    <t>0.3609,0.0936,0.6195,0.0035</t>
+  </si>
+  <si>
+    <t>0.4353,0.0671,0.5919,0.0021</t>
+  </si>
+  <si>
+    <t>0.0891,0.8415,0.1063,0.0019</t>
+  </si>
+  <si>
+    <t>0.1275,0.5299,0.3951,0.0024</t>
+  </si>
+  <si>
+    <t>0.6839,0.0938,0.3066,0.0142</t>
+  </si>
+  <si>
+    <t>0.6588,0.2253,0.2196,0.0297</t>
+  </si>
+  <si>
+    <t>0.5391,0.3055,0.2376,0.0192</t>
+  </si>
+  <si>
+    <t>0.4513,0.3150,0.4158,0.0819</t>
+  </si>
+  <si>
+    <t>0.6331,0.2243,0.2480,0.0401</t>
+  </si>
+  <si>
+    <t>0.7304,0.1189,0.2307,0.0207</t>
+  </si>
+  <si>
+    <t>0.0770,0.4946,0.5771,0.0015</t>
+  </si>
+  <si>
+    <t>0.3113,0.0712,0.6872,0.0021</t>
+  </si>
+  <si>
+    <t>0.2046,0.1974,0.6436,0.0028</t>
+  </si>
+  <si>
+    <t>0.3663,0.0828,0.6123,0.0036</t>
+  </si>
+  <si>
+    <t>0.3216,0.1946,0.4159,0.0013</t>
+  </si>
+  <si>
+    <t>0.4785,0.1889,0.3170,0.0039</t>
+  </si>
+  <si>
+    <t>0.3213,0.6053,0.1566,0.0125</t>
+  </si>
+  <si>
+    <t>0.4295,0.5518,0.1154,0.0283</t>
+  </si>
+  <si>
+    <t>0.3105,0.6739,0.0915,0.0162</t>
+  </si>
+  <si>
+    <t>0.3603,0.6273,0.1130,0.0297</t>
+  </si>
+  <si>
+    <t>0.5480,0.4759,0.0531,0.0132</t>
+  </si>
+  <si>
+    <t>0.6298,0.3590,0.0960,0.0101</t>
+  </si>
+  <si>
+    <t>0.4808,0.5242,0.0914,0.0197</t>
+  </si>
+  <si>
+    <t>0.3440,0.6377,0.1200,0.0282</t>
+  </si>
+  <si>
+    <t>0.4266,0.5593,0.1131,0.0265</t>
+  </si>
+  <si>
+    <t>0.3795,0.6428,0.0676,0.0187</t>
+  </si>
+  <si>
+    <t>0.5418,0.4458,0.0961,0.0202</t>
+  </si>
+  <si>
+    <t>0.4581,0.5263,0.1222,0.0209</t>
+  </si>
+  <si>
+    <t>0.4063,0.5552,0.1222,0.0143</t>
+  </si>
+  <si>
+    <t>0.3570,0.6520,0.0806,0.0200</t>
+  </si>
+  <si>
+    <t>0.3726,0.5946,0.1522,0.0248</t>
+  </si>
+  <si>
+    <t>0.3859,0.5790,0.1018,0.0129</t>
+  </si>
+  <si>
+    <t>0.0180,0.0946,0.9702,0.0011</t>
+  </si>
+  <si>
+    <t>0.6427,0.0420,0.4354,0.0039</t>
+  </si>
+  <si>
+    <t>0.6207,0.0939,0.3292,0.0062</t>
+  </si>
+  <si>
+    <t>0.4769,0.0626,0.5760,0.0076</t>
+  </si>
+  <si>
+    <t>0.1760,0.8066,0.0851,0.0152</t>
+  </si>
+  <si>
+    <t>0.3619,0.6105,0.0950,0.0088</t>
+  </si>
+  <si>
+    <t>0.2602,0.6948,0.0885,0.0089</t>
+  </si>
+  <si>
+    <t>0.3040,0.6701,0.0975,0.0142</t>
+  </si>
+  <si>
+    <t>0.4000,0.5867,0.0912,0.0138</t>
+  </si>
+  <si>
+    <t>0.3524,0.6262,0.0847,0.0076</t>
+  </si>
+  <si>
+    <t>0.4936,0.4834,0.1039,0.0136</t>
+  </si>
+  <si>
+    <t>0.6086,0.2187,0.2453,0.0163</t>
+  </si>
+  <si>
+    <t>0.6059,0.1218,0.3675,0.0102</t>
+  </si>
+  <si>
+    <t>0.5129,0.1881,0.2870,0.0043</t>
+  </si>
+  <si>
+    <t>0.6410,0.1436,0.2406,0.0062</t>
+  </si>
+  <si>
+    <t>0.5021,0.3060,0.2545,0.0087</t>
+  </si>
+  <si>
+    <t>0.4493,0.4141,0.1473,0.0065</t>
+  </si>
+  <si>
+    <t>0.3401,0.3685,0.2614,0.0059</t>
+  </si>
+  <si>
+    <t>0.4325,0.4096,0.1827,0.0085</t>
+  </si>
+  <si>
+    <t>0.0486,0.9297,0.0326,0.0019</t>
+  </si>
+  <si>
+    <t>0.3551,0.5390,0.1487,0.0067</t>
+  </si>
+  <si>
+    <t>0.4813,0.4758,0.1435,0.0204</t>
+  </si>
+  <si>
+    <t>0.2973,0.6240,0.1307,0.0074</t>
+  </si>
+  <si>
+    <t>0.4831,0.4328,0.1758,0.0206</t>
+  </si>
+  <si>
+    <t>0.5204,0.4909,0.0817,0.0193</t>
+  </si>
+  <si>
+    <t>0.5968,0.4067,0.0710,0.0097</t>
+  </si>
+  <si>
+    <t>0.3718,0.5968,0.1142,0.0159</t>
+  </si>
+  <si>
+    <t>0.3569,0.5862,0.1362,0.0140</t>
+  </si>
+  <si>
+    <t>0.5448,0.4066,0.1271,0.0149</t>
+  </si>
+  <si>
+    <t>0.4015,0.5705,0.1094,0.0202</t>
+  </si>
+  <si>
+    <t>0.2916,0.6329,0.1396,0.0159</t>
+  </si>
+  <si>
+    <t>0.2910,0.1373,0.6511,0.0045</t>
+  </si>
+  <si>
+    <t>0.4424,0.0783,0.4923,0.0027</t>
+  </si>
+  <si>
+    <t>0.2277,0.0718,0.7575,0.0026</t>
+  </si>
+  <si>
+    <t>0.5437,0.0952,0.4215,0.0041</t>
+  </si>
+  <si>
+    <t>0.7341,0.1030,0.2134,0.0067</t>
+  </si>
+  <si>
+    <t>0.6481,0.1358,0.2754,0.0087</t>
+  </si>
+  <si>
+    <t>0.4677,0.1261,0.4270,0.0049</t>
+  </si>
+  <si>
+    <t>0.6910,0.0643,0.3312,0.0041</t>
+  </si>
+  <si>
+    <t>0.5936,0.2386,0.2345,0.0144</t>
+  </si>
+  <si>
+    <t>0.6299,0.2153,0.2159,0.0314</t>
+  </si>
+  <si>
+    <t>0.5077,0.3444,0.2351,0.0234</t>
+  </si>
+  <si>
+    <t>0.5927,0.2671,0.2474,0.0294</t>
+  </si>
+  <si>
+    <t>0.2090,0.5439,0.2620,0.0052</t>
+  </si>
+  <si>
+    <t>0.4045,0.5395,0.1452,0.0129</t>
+  </si>
+  <si>
+    <t>0.3881,0.5795,0.1283,0.0236</t>
+  </si>
+  <si>
+    <t>0.3625,0.5755,0.1471,0.0118</t>
+  </si>
+  <si>
+    <t>0.4075,0.5752,0.1106,0.0169</t>
+  </si>
+  <si>
+    <t>0.5514,0.3770,0.1160,0.0069</t>
+  </si>
+  <si>
+    <t>0.4564,0.3952,0.2335,0.0139</t>
+  </si>
+  <si>
+    <t>0.6382,0.2954,0.1556,0.0190</t>
+  </si>
+  <si>
+    <t>0.0451,0.5440,0.8027,0.0082</t>
+  </si>
+  <si>
+    <t>0.5683,0.4145,0.0992,0.0208</t>
+  </si>
+  <si>
+    <t>0.3945,0.5400,0.1554,0.0194</t>
+  </si>
+  <si>
+    <t>0.4340,0.4386,0.1634,0.0100</t>
+  </si>
+  <si>
+    <t>0.5354,0.3940,0.1524,0.0171</t>
+  </si>
+  <si>
+    <t>0.4738,0.4539,0.1582,0.0130</t>
+  </si>
+  <si>
+    <t>0.4604,0.4159,0.2080,0.0207</t>
+  </si>
+  <si>
+    <t>0.3236,0.5988,0.1394,0.0106</t>
+  </si>
+  <si>
+    <t>0.5135,0.3700,0.2165,0.0201</t>
+  </si>
+  <si>
+    <t>0.6783,0.2752,0.1182,0.0200</t>
+  </si>
+  <si>
+    <t>0.4507,0.5707,0.0779,0.0234</t>
+  </si>
+  <si>
+    <t>0.3981,0.5261,0.1843,0.0185</t>
+  </si>
+  <si>
+    <t>0.4227,0.5402,0.1437,0.0231</t>
+  </si>
+  <si>
+    <t>0.5253,0.4133,0.1421,0.0137</t>
+  </si>
+  <si>
+    <t>0.4475,0.5357,0.1186,0.0190</t>
+  </si>
+  <si>
+    <t>0.4285,0.5502,0.1493,0.0309</t>
+  </si>
+  <si>
+    <t>0.4249,0.5735,0.0998,0.0298</t>
+  </si>
+  <si>
+    <t>0.6017,0.3448,0.1092,0.0081</t>
+  </si>
+  <si>
+    <t>0.2676,0.6930,0.1018,0.0126</t>
+  </si>
+  <si>
+    <t>0.3295,0.6536,0.1007,0.0113</t>
+  </si>
+  <si>
+    <t>0.3521,0.2436,0.5159,0.0152</t>
+  </si>
+  <si>
+    <t>0.2969,0.6659,0.1307,0.0216</t>
+  </si>
+  <si>
+    <t>0.3913,0.4537,0.1901,0.0081</t>
+  </si>
+  <si>
+    <t>0.4108,0.5719,0.1099,0.0136</t>
+  </si>
+  <si>
+    <t>0.2661,0.5717,0.2338,0.0135</t>
+  </si>
+  <si>
+    <t>0.0959,0.2202,0.8260,0.0030</t>
+  </si>
+  <si>
+    <t>0.5220,0.4615,0.1082,0.0117</t>
+  </si>
+  <si>
+    <t>0.1774,0.0861,0.7911,0.0034</t>
+  </si>
+  <si>
+    <t>0.4479,0.0931,0.5722,0.0046</t>
+  </si>
+  <si>
+    <t>0.5709,0.1704,0.3049,0.0082</t>
+  </si>
+  <si>
+    <t>0.2006,0.0612,0.8144,0.0031</t>
+  </si>
+  <si>
+    <t>0.5487,0.0797,0.4934,0.0058</t>
+  </si>
+  <si>
+    <t>0.1374,0.0420,0.8951,0.0018</t>
+  </si>
+  <si>
+    <t>0.5071,0.0681,0.5372,0.0060</t>
+  </si>
+  <si>
+    <t>0.4041,0.3083,0.3216,0.0100</t>
+  </si>
+  <si>
+    <t>0.4360,0.2778,0.3197,0.0099</t>
+  </si>
+  <si>
+    <t>0.4168,0.2565,0.3700,0.0098</t>
+  </si>
+  <si>
+    <t>0.3713,0.3347,0.2943,0.0073</t>
+  </si>
+  <si>
+    <t>0.3773,0.2515,0.3671,0.0048</t>
+  </si>
+  <si>
+    <t>0.4104,0.2410,0.3413,0.0049</t>
+  </si>
+  <si>
+    <t>0.6071,0.1520,0.2805,0.0088</t>
+  </si>
+  <si>
+    <t>0.5379,0.1783,0.3134,0.0074</t>
+  </si>
+  <si>
+    <t>0.3185,0.6784,0.0855,0.0167</t>
+  </si>
+  <si>
+    <t>0.3972,0.5983,0.0848,0.0101</t>
+  </si>
+  <si>
+    <t>0.2997,0.6782,0.1158,0.0172</t>
+  </si>
+  <si>
+    <t>0.4693,0.5256,0.1144,0.0161</t>
+  </si>
+  <si>
+    <t>0.5302,0.4550,0.1035,0.0156</t>
+  </si>
+  <si>
+    <t>0.4971,0.2194,0.3444,0.0105</t>
+  </si>
+  <si>
+    <t>0.6562,0.1090,0.3007,0.0069</t>
+  </si>
+  <si>
+    <t>0.6376,0.1564,0.2965,0.0159</t>
+  </si>
+  <si>
+    <t>0.4788,0.2327,0.3257,0.0111</t>
+  </si>
+  <si>
+    <t>0.6523,0.1776,0.2222,0.0134</t>
+  </si>
+  <si>
+    <t>0.0889,0.0821,0.8758,0.0016</t>
+  </si>
+  <si>
+    <t>0.7128,0.0436,0.3431,0.0034</t>
+  </si>
+  <si>
+    <t>0.6481,0.0499,0.4230,0.0020</t>
+  </si>
+  <si>
+    <t>0.5772,0.0509,0.4758,0.0021</t>
+  </si>
+  <si>
+    <t>0.4096,0.1750,0.3420,0.0028</t>
+  </si>
+  <si>
+    <t>0.5435,0.4123,0.1432,0.0330</t>
+  </si>
+  <si>
+    <t>0.3615,0.6163,0.0919,0.0107</t>
+  </si>
+  <si>
+    <t>0.3162,0.6537,0.1092,0.0143</t>
+  </si>
+  <si>
+    <t>0.3385,0.6671,0.0829,0.0139</t>
+  </si>
+  <si>
+    <t>0.3085,0.6625,0.1189,0.0153</t>
+  </si>
+  <si>
+    <t>0.5203,0.4453,0.1266,0.0227</t>
+  </si>
+  <si>
+    <t>0.5562,0.4022,0.1151,0.0198</t>
+  </si>
+  <si>
+    <t>0.4630,0.4657,0.1592,0.0170</t>
+  </si>
+  <si>
+    <t>0.3705,0.3047,0.3561,0.0105</t>
+  </si>
+  <si>
+    <t>0.4485,0.4201,0.1920,0.0111</t>
+  </si>
+  <si>
+    <t>0.5801,0.3582,0.1500,0.0185</t>
+  </si>
+  <si>
+    <t>0.3253,0.0518,0.7221,0.0034</t>
+  </si>
+  <si>
+    <t>0.2601,0.0468,0.7879,0.0028</t>
+  </si>
+  <si>
+    <t>0.5428,0.0380,0.5963,0.0046</t>
+  </si>
+  <si>
+    <t>0.0250,0.0669,0.9699,0.0012</t>
+  </si>
+  <si>
+    <t>0.5767,0.0702,0.4846,0.0043</t>
+  </si>
+  <si>
+    <t>0.0057,0.1223,0.9870,0.0005</t>
+  </si>
+  <si>
+    <t>0.4923,0.0425,0.6258,0.0028</t>
+  </si>
+  <si>
+    <t>0.7180,0.1082,0.2106,0.0062</t>
+  </si>
+  <si>
+    <t>0.5205,0.2055,0.3289,0.0126</t>
+  </si>
+  <si>
+    <t>0.6135,0.0825,0.3593,0.0048</t>
+  </si>
+  <si>
+    <t>0.6065,0.1043,0.3473,0.0050</t>
+  </si>
+  <si>
+    <t>0.4988,0.5106,0.0761,0.0135</t>
+  </si>
+  <si>
+    <t>0.4427,0.5441,0.1020,0.0138</t>
+  </si>
+  <si>
+    <t>0.4332,0.5830,0.0833,0.0110</t>
+  </si>
+  <si>
+    <t>0.6543,0.3274,0.0969,0.0158</t>
+  </si>
+  <si>
+    <t>0.4345,0.5713,0.0883,0.0236</t>
+  </si>
+  <si>
+    <t>0.4578,0.5568,0.0800,0.0188</t>
+  </si>
+  <si>
+    <t>0.4691,0.5273,0.0916,0.0162</t>
+  </si>
+  <si>
+    <t>0.5150,0.5115,0.0764,0.0297</t>
+  </si>
+  <si>
+    <t>0.3261,0.2717,0.3878,0.0055</t>
+  </si>
+  <si>
+    <t>0.0427,0.0749,0.9365,0.0011</t>
+  </si>
+  <si>
+    <t>0.1564,0.0728,0.8630,0.0028</t>
+  </si>
+  <si>
+    <t>0.6252,0.0443,0.4596,0.0042</t>
+  </si>
+  <si>
+    <t>0.5956,0.0181,0.5788,0.0026</t>
+  </si>
+  <si>
+    <t>0.5257,0.1400,0.4304,0.0089</t>
+  </si>
+  <si>
+    <t>0.6823,0.0919,0.2995,0.0057</t>
+  </si>
+  <si>
+    <t>0.4767,0.0814,0.4870,0.0038</t>
+  </si>
+  <si>
+    <t>0.6591,0.2130,0.1500,0.0091</t>
+  </si>
+  <si>
+    <t>0.5359,0.3140,0.2435,0.0219</t>
+  </si>
+  <si>
+    <t>0.7612,0.0838,0.2186,0.0139</t>
+  </si>
+  <si>
+    <t>0.4535,0.4225,0.2382,0.0298</t>
+  </si>
+  <si>
+    <t>0.7293,0.1809,0.1391,0.0190</t>
+  </si>
+  <si>
+    <t>0.4139,0.4217,0.1922,0.0098</t>
   </si>
 </sst>
 </file>
@@ -1981,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
         <v>266</v>
@@ -2009,7 +2009,7 @@
         <v>259</v>
       </c>
       <c r="C6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
         <v>268</v>
@@ -2023,7 +2023,7 @@
         <v>259</v>
       </c>
       <c r="C7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D7" t="s">
         <v>269</v>
@@ -2065,7 +2065,7 @@
         <v>259</v>
       </c>
       <c r="C10" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D10" t="s">
         <v>272</v>
@@ -2093,7 +2093,7 @@
         <v>259</v>
       </c>
       <c r="C12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D12" t="s">
         <v>274</v>
@@ -2107,7 +2107,7 @@
         <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D13" t="s">
         <v>275</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2709,7 +2709,7 @@
         <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D56" t="s">
         <v>318</v>
@@ -2723,7 +2723,7 @@
         <v>259</v>
       </c>
       <c r="C57" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D57" t="s">
         <v>319</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2765,7 +2765,7 @@
         <v>259</v>
       </c>
       <c r="C60" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D60" t="s">
         <v>322</v>
@@ -2793,7 +2793,7 @@
         <v>259</v>
       </c>
       <c r="C62" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D62" t="s">
         <v>324</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3213,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="C92" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D92" t="s">
         <v>354</v>
@@ -3227,7 +3227,7 @@
         <v>259</v>
       </c>
       <c r="C93" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D93" t="s">
         <v>355</v>
@@ -3241,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D94" t="s">
         <v>356</v>
@@ -3325,7 +3325,7 @@
         <v>259</v>
       </c>
       <c r="C100" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D100" t="s">
         <v>362</v>
@@ -3339,7 +3339,7 @@
         <v>259</v>
       </c>
       <c r="C101" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D101" t="s">
         <v>363</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3689,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
         <v>388</v>
@@ -3717,7 +3717,7 @@
         <v>259</v>
       </c>
       <c r="C128" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D128" t="s">
         <v>390</v>
@@ -3745,7 +3745,7 @@
         <v>259</v>
       </c>
       <c r="C130" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D130" t="s">
         <v>392</v>
@@ -3773,7 +3773,7 @@
         <v>259</v>
       </c>
       <c r="C132" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D132" t="s">
         <v>394</v>
@@ -3801,7 +3801,7 @@
         <v>259</v>
       </c>
       <c r="C134" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D134" t="s">
         <v>396</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4011,7 +4011,7 @@
         <v>259</v>
       </c>
       <c r="C149" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D149" t="s">
         <v>411</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4039,7 +4039,7 @@
         <v>259</v>
       </c>
       <c r="C151" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D151" t="s">
         <v>413</v>
@@ -4095,7 +4095,7 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D155" t="s">
         <v>417</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4207,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
         <v>425</v>
@@ -4221,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D164" t="s">
         <v>426</v>
@@ -4235,7 +4235,7 @@
         <v>259</v>
       </c>
       <c r="C165" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D165" t="s">
         <v>427</v>
@@ -4291,7 +4291,7 @@
         <v>259</v>
       </c>
       <c r="C169" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D169" t="s">
         <v>431</v>
@@ -4319,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="C171" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D171" t="s">
         <v>433</v>
@@ -4347,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
         <v>435</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4431,7 +4431,7 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D179" t="s">
         <v>441</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -4907,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="C213" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D213" t="s">
         <v>475</v>
@@ -4977,7 +4977,7 @@
         <v>259</v>
       </c>
       <c r="C218" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D218" t="s">
         <v>480</v>
@@ -5005,7 +5005,7 @@
         <v>259</v>
       </c>
       <c r="C220" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D220" t="s">
         <v>482</v>
@@ -5047,7 +5047,7 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
         <v>485</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5215,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="C235" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D235" t="s">
         <v>497</v>
@@ -5243,7 +5243,7 @@
         <v>259</v>
       </c>
       <c r="C237" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D237" t="s">
         <v>499</v>
@@ -5257,7 +5257,7 @@
         <v>259</v>
       </c>
       <c r="C238" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D238" t="s">
         <v>500</v>
@@ -5285,7 +5285,7 @@
         <v>259</v>
       </c>
       <c r="C240" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D240" t="s">
         <v>502</v>
@@ -5313,7 +5313,7 @@
         <v>259</v>
       </c>
       <c r="C242" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D242" t="s">
         <v>504</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6050,0.1683,0.2573,0.0075</t>
-  </si>
-  <si>
-    <t>0.7056,0.1709,0.1807,0.0145</t>
-  </si>
-  <si>
-    <t>0.4350,0.4705,0.1902,0.0262</t>
-  </si>
-  <si>
-    <t>0.4676,0.3890,0.1822,0.0109</t>
-  </si>
-  <si>
-    <t>0.6521,0.3109,0.0948,0.0356</t>
-  </si>
-  <si>
-    <t>0.4911,0.4932,0.1003,0.0223</t>
-  </si>
-  <si>
-    <t>0.2694,0.7001,0.0855,0.0118</t>
-  </si>
-  <si>
-    <t>0.3052,0.6547,0.1264,0.0187</t>
-  </si>
-  <si>
-    <t>0.3037,0.6765,0.1051,0.0141</t>
-  </si>
-  <si>
-    <t>0.3651,0.6255,0.1218,0.0266</t>
-  </si>
-  <si>
-    <t>0.4681,0.5579,0.0772,0.0239</t>
-  </si>
-  <si>
-    <t>0.4416,0.5760,0.0859,0.0211</t>
-  </si>
-  <si>
-    <t>0.6146,0.1121,0.3403,0.0062</t>
-  </si>
-  <si>
-    <t>0.4709,0.1553,0.4223,0.0075</t>
-  </si>
-  <si>
-    <t>0.6547,0.0865,0.3461,0.0081</t>
-  </si>
-  <si>
-    <t>0.5880,0.1698,0.2669,0.0055</t>
-  </si>
-  <si>
-    <t>0.4528,0.2881,0.2605,0.0071</t>
-  </si>
-  <si>
-    <t>0.4525,0.4836,0.1403,0.0119</t>
-  </si>
-  <si>
-    <t>0.3602,0.5535,0.1448,0.0094</t>
-  </si>
-  <si>
-    <t>0.4261,0.4488,0.2105,0.0147</t>
-  </si>
-  <si>
-    <t>0.1769,0.8006,0.0797,0.0072</t>
-  </si>
-  <si>
-    <t>0.3076,0.6439,0.0868,0.0071</t>
-  </si>
-  <si>
-    <t>0.5615,0.1388,0.3724,0.0090</t>
-  </si>
-  <si>
-    <t>0.7002,0.0332,0.3908,0.0046</t>
-  </si>
-  <si>
-    <t>0.3997,0.0504,0.6587,0.0060</t>
-  </si>
-  <si>
-    <t>0.6400,0.0663,0.3817,0.0043</t>
-  </si>
-  <si>
-    <t>0.3649,0.1639,0.5231,0.0057</t>
-  </si>
-  <si>
-    <t>0.5424,0.1157,0.4175,0.0070</t>
-  </si>
-  <si>
-    <t>0.1127,0.0387,0.9165,0.0021</t>
-  </si>
-  <si>
-    <t>0.3748,0.4726,0.1543,0.0044</t>
-  </si>
-  <si>
-    <t>0.2334,0.5684,0.2434,0.0100</t>
-  </si>
-  <si>
-    <t>0.0359,0.4796,0.8638,0.0071</t>
-  </si>
-  <si>
-    <t>0.3226,0.4866,0.1629,0.0049</t>
-  </si>
-  <si>
-    <t>0.5269,0.4025,0.1618,0.0294</t>
-  </si>
-  <si>
-    <t>0.3595,0.5679,0.1703,0.0244</t>
-  </si>
-  <si>
-    <t>0.6085,0.3889,0.0563,0.0057</t>
-  </si>
-  <si>
-    <t>0.4433,0.5020,0.1289,0.0105</t>
-  </si>
-  <si>
-    <t>0.2621,0.1010,0.7007,0.0034</t>
-  </si>
-  <si>
-    <t>0.6126,0.0338,0.5281,0.0049</t>
-  </si>
-  <si>
-    <t>0.6868,0.0414,0.4014,0.0016</t>
-  </si>
-  <si>
-    <t>0.5650,0.0213,0.6016,0.0034</t>
-  </si>
-  <si>
-    <t>0.5222,0.0979,0.3986,0.0035</t>
-  </si>
-  <si>
-    <t>0.0638,0.9117,0.0383,0.0008</t>
-  </si>
-  <si>
-    <t>0.5008,0.0500,0.5599,0.0037</t>
-  </si>
-  <si>
-    <t>0.4357,0.4920,0.1603,0.0131</t>
-  </si>
-  <si>
-    <t>0.2029,0.7069,0.1136,0.0044</t>
-  </si>
-  <si>
-    <t>0.4042,0.3997,0.2185,0.0069</t>
-  </si>
-  <si>
-    <t>0.3176,0.5491,0.1406,0.0058</t>
-  </si>
-  <si>
-    <t>0.0566,0.2949,0.8685,0.0048</t>
-  </si>
-  <si>
-    <t>0.1759,0.0482,0.8411,0.0016</t>
-  </si>
-  <si>
-    <t>0.4681,0.1946,0.3250,0.0042</t>
-  </si>
-  <si>
-    <t>0.5563,0.1148,0.3949,0.0060</t>
-  </si>
-  <si>
-    <t>0.1235,0.0836,0.8382,0.0021</t>
-  </si>
-  <si>
-    <t>0.4813,0.0562,0.5738,0.0036</t>
-  </si>
-  <si>
-    <t>0.3157,0.6349,0.1240,0.0146</t>
-  </si>
-  <si>
-    <t>0.4639,0.5078,0.1092,0.0188</t>
-  </si>
-  <si>
-    <t>0.4306,0.5671,0.0821,0.0180</t>
-  </si>
-  <si>
-    <t>0.0587,0.8632,0.1591,0.0063</t>
-  </si>
-  <si>
-    <t>0.4539,0.4677,0.1741,0.0211</t>
-  </si>
-  <si>
-    <t>0.3514,0.6530,0.0723,0.0152</t>
-  </si>
-  <si>
-    <t>0.3689,0.5950,0.1336,0.0142</t>
-  </si>
-  <si>
-    <t>0.2532,0.2671,0.5223,0.0031</t>
-  </si>
-  <si>
-    <t>0.3410,0.0775,0.6749,0.0049</t>
-  </si>
-  <si>
-    <t>0.0721,0.2839,0.7697,0.0021</t>
-  </si>
-  <si>
-    <t>0.1807,0.3692,0.4669,0.0030</t>
-  </si>
-  <si>
-    <t>0.3044,0.0326,0.7832,0.0026</t>
-  </si>
-  <si>
-    <t>0.3380,0.5910,0.0886,0.0052</t>
-  </si>
-  <si>
-    <t>0.0340,0.9578,0.0163,0.0016</t>
-  </si>
-  <si>
-    <t>0.4212,0.3429,0.2296,0.0042</t>
-  </si>
-  <si>
-    <t>0.2950,0.5830,0.2024,0.0137</t>
-  </si>
-  <si>
-    <t>0.1214,0.6807,0.2625,0.0036</t>
-  </si>
-  <si>
-    <t>0.3609,0.0936,0.6195,0.0035</t>
-  </si>
-  <si>
-    <t>0.4353,0.0671,0.5919,0.0021</t>
-  </si>
-  <si>
-    <t>0.0891,0.8415,0.1063,0.0019</t>
-  </si>
-  <si>
-    <t>0.1275,0.5299,0.3951,0.0024</t>
-  </si>
-  <si>
-    <t>0.6839,0.0938,0.3066,0.0142</t>
-  </si>
-  <si>
-    <t>0.6588,0.2253,0.2196,0.0297</t>
-  </si>
-  <si>
-    <t>0.5391,0.3055,0.2376,0.0192</t>
-  </si>
-  <si>
-    <t>0.4513,0.3150,0.4158,0.0819</t>
-  </si>
-  <si>
-    <t>0.6331,0.2243,0.2480,0.0401</t>
-  </si>
-  <si>
-    <t>0.7304,0.1189,0.2307,0.0207</t>
-  </si>
-  <si>
-    <t>0.0770,0.4946,0.5771,0.0015</t>
-  </si>
-  <si>
-    <t>0.3113,0.0712,0.6872,0.0021</t>
-  </si>
-  <si>
-    <t>0.2046,0.1974,0.6436,0.0028</t>
-  </si>
-  <si>
-    <t>0.3663,0.0828,0.6123,0.0036</t>
-  </si>
-  <si>
-    <t>0.3216,0.1946,0.4159,0.0013</t>
-  </si>
-  <si>
-    <t>0.4785,0.1889,0.3170,0.0039</t>
-  </si>
-  <si>
-    <t>0.3213,0.6053,0.1566,0.0125</t>
-  </si>
-  <si>
-    <t>0.4295,0.5518,0.1154,0.0283</t>
-  </si>
-  <si>
-    <t>0.3105,0.6739,0.0915,0.0162</t>
-  </si>
-  <si>
-    <t>0.3603,0.6273,0.1130,0.0297</t>
-  </si>
-  <si>
-    <t>0.5480,0.4759,0.0531,0.0132</t>
-  </si>
-  <si>
-    <t>0.6298,0.3590,0.0960,0.0101</t>
-  </si>
-  <si>
-    <t>0.4808,0.5242,0.0914,0.0197</t>
-  </si>
-  <si>
-    <t>0.3440,0.6377,0.1200,0.0282</t>
-  </si>
-  <si>
-    <t>0.4266,0.5593,0.1131,0.0265</t>
-  </si>
-  <si>
-    <t>0.3795,0.6428,0.0676,0.0187</t>
-  </si>
-  <si>
-    <t>0.5418,0.4458,0.0961,0.0202</t>
-  </si>
-  <si>
-    <t>0.4581,0.5263,0.1222,0.0209</t>
-  </si>
-  <si>
-    <t>0.4063,0.5552,0.1222,0.0143</t>
-  </si>
-  <si>
-    <t>0.3570,0.6520,0.0806,0.0200</t>
-  </si>
-  <si>
-    <t>0.3726,0.5946,0.1522,0.0248</t>
-  </si>
-  <si>
-    <t>0.3859,0.5790,0.1018,0.0129</t>
-  </si>
-  <si>
-    <t>0.0180,0.0946,0.9702,0.0011</t>
-  </si>
-  <si>
-    <t>0.6427,0.0420,0.4354,0.0039</t>
-  </si>
-  <si>
-    <t>0.6207,0.0939,0.3292,0.0062</t>
-  </si>
-  <si>
-    <t>0.4769,0.0626,0.5760,0.0076</t>
-  </si>
-  <si>
-    <t>0.1760,0.8066,0.0851,0.0152</t>
-  </si>
-  <si>
-    <t>0.3619,0.6105,0.0950,0.0088</t>
-  </si>
-  <si>
-    <t>0.2602,0.6948,0.0885,0.0089</t>
-  </si>
-  <si>
-    <t>0.3040,0.6701,0.0975,0.0142</t>
-  </si>
-  <si>
-    <t>0.4000,0.5867,0.0912,0.0138</t>
-  </si>
-  <si>
-    <t>0.3524,0.6262,0.0847,0.0076</t>
-  </si>
-  <si>
-    <t>0.4936,0.4834,0.1039,0.0136</t>
-  </si>
-  <si>
-    <t>0.6086,0.2187,0.2453,0.0163</t>
-  </si>
-  <si>
-    <t>0.6059,0.1218,0.3675,0.0102</t>
-  </si>
-  <si>
-    <t>0.5129,0.1881,0.2870,0.0043</t>
-  </si>
-  <si>
-    <t>0.6410,0.1436,0.2406,0.0062</t>
-  </si>
-  <si>
-    <t>0.5021,0.3060,0.2545,0.0087</t>
-  </si>
-  <si>
-    <t>0.4493,0.4141,0.1473,0.0065</t>
-  </si>
-  <si>
-    <t>0.3401,0.3685,0.2614,0.0059</t>
-  </si>
-  <si>
-    <t>0.4325,0.4096,0.1827,0.0085</t>
-  </si>
-  <si>
-    <t>0.0486,0.9297,0.0326,0.0019</t>
-  </si>
-  <si>
-    <t>0.3551,0.5390,0.1487,0.0067</t>
-  </si>
-  <si>
-    <t>0.4813,0.4758,0.1435,0.0204</t>
-  </si>
-  <si>
-    <t>0.2973,0.6240,0.1307,0.0074</t>
-  </si>
-  <si>
-    <t>0.4831,0.4328,0.1758,0.0206</t>
-  </si>
-  <si>
-    <t>0.5204,0.4909,0.0817,0.0193</t>
-  </si>
-  <si>
-    <t>0.5968,0.4067,0.0710,0.0097</t>
-  </si>
-  <si>
-    <t>0.3718,0.5968,0.1142,0.0159</t>
-  </si>
-  <si>
-    <t>0.3569,0.5862,0.1362,0.0140</t>
-  </si>
-  <si>
-    <t>0.5448,0.4066,0.1271,0.0149</t>
-  </si>
-  <si>
-    <t>0.4015,0.5705,0.1094,0.0202</t>
-  </si>
-  <si>
-    <t>0.2916,0.6329,0.1396,0.0159</t>
-  </si>
-  <si>
-    <t>0.2910,0.1373,0.6511,0.0045</t>
-  </si>
-  <si>
-    <t>0.4424,0.0783,0.4923,0.0027</t>
-  </si>
-  <si>
-    <t>0.2277,0.0718,0.7575,0.0026</t>
-  </si>
-  <si>
-    <t>0.5437,0.0952,0.4215,0.0041</t>
-  </si>
-  <si>
-    <t>0.7341,0.1030,0.2134,0.0067</t>
-  </si>
-  <si>
-    <t>0.6481,0.1358,0.2754,0.0087</t>
-  </si>
-  <si>
-    <t>0.4677,0.1261,0.4270,0.0049</t>
-  </si>
-  <si>
-    <t>0.6910,0.0643,0.3312,0.0041</t>
-  </si>
-  <si>
-    <t>0.5936,0.2386,0.2345,0.0144</t>
-  </si>
-  <si>
-    <t>0.6299,0.2153,0.2159,0.0314</t>
-  </si>
-  <si>
-    <t>0.5077,0.3444,0.2351,0.0234</t>
-  </si>
-  <si>
-    <t>0.5927,0.2671,0.2474,0.0294</t>
-  </si>
-  <si>
-    <t>0.2090,0.5439,0.2620,0.0052</t>
-  </si>
-  <si>
-    <t>0.4045,0.5395,0.1452,0.0129</t>
-  </si>
-  <si>
-    <t>0.3881,0.5795,0.1283,0.0236</t>
-  </si>
-  <si>
-    <t>0.3625,0.5755,0.1471,0.0118</t>
-  </si>
-  <si>
-    <t>0.4075,0.5752,0.1106,0.0169</t>
-  </si>
-  <si>
-    <t>0.5514,0.3770,0.1160,0.0069</t>
-  </si>
-  <si>
-    <t>0.4564,0.3952,0.2335,0.0139</t>
-  </si>
-  <si>
-    <t>0.6382,0.2954,0.1556,0.0190</t>
-  </si>
-  <si>
-    <t>0.0451,0.5440,0.8027,0.0082</t>
-  </si>
-  <si>
-    <t>0.5683,0.4145,0.0992,0.0208</t>
-  </si>
-  <si>
-    <t>0.3945,0.5400,0.1554,0.0194</t>
-  </si>
-  <si>
-    <t>0.4340,0.4386,0.1634,0.0100</t>
-  </si>
-  <si>
-    <t>0.5354,0.3940,0.1524,0.0171</t>
-  </si>
-  <si>
-    <t>0.4738,0.4539,0.1582,0.0130</t>
-  </si>
-  <si>
-    <t>0.4604,0.4159,0.2080,0.0207</t>
-  </si>
-  <si>
-    <t>0.3236,0.5988,0.1394,0.0106</t>
-  </si>
-  <si>
-    <t>0.5135,0.3700,0.2165,0.0201</t>
-  </si>
-  <si>
-    <t>0.6783,0.2752,0.1182,0.0200</t>
-  </si>
-  <si>
-    <t>0.4507,0.5707,0.0779,0.0234</t>
-  </si>
-  <si>
-    <t>0.3981,0.5261,0.1843,0.0185</t>
-  </si>
-  <si>
-    <t>0.4227,0.5402,0.1437,0.0231</t>
-  </si>
-  <si>
-    <t>0.5253,0.4133,0.1421,0.0137</t>
-  </si>
-  <si>
-    <t>0.4475,0.5357,0.1186,0.0190</t>
-  </si>
-  <si>
-    <t>0.4285,0.5502,0.1493,0.0309</t>
-  </si>
-  <si>
-    <t>0.4249,0.5735,0.0998,0.0298</t>
-  </si>
-  <si>
-    <t>0.6017,0.3448,0.1092,0.0081</t>
-  </si>
-  <si>
-    <t>0.2676,0.6930,0.1018,0.0126</t>
-  </si>
-  <si>
-    <t>0.3295,0.6536,0.1007,0.0113</t>
-  </si>
-  <si>
-    <t>0.3521,0.2436,0.5159,0.0152</t>
-  </si>
-  <si>
-    <t>0.2969,0.6659,0.1307,0.0216</t>
-  </si>
-  <si>
-    <t>0.3913,0.4537,0.1901,0.0081</t>
-  </si>
-  <si>
-    <t>0.4108,0.5719,0.1099,0.0136</t>
-  </si>
-  <si>
-    <t>0.2661,0.5717,0.2338,0.0135</t>
-  </si>
-  <si>
-    <t>0.0959,0.2202,0.8260,0.0030</t>
-  </si>
-  <si>
-    <t>0.5220,0.4615,0.1082,0.0117</t>
-  </si>
-  <si>
-    <t>0.1774,0.0861,0.7911,0.0034</t>
-  </si>
-  <si>
-    <t>0.4479,0.0931,0.5722,0.0046</t>
-  </si>
-  <si>
-    <t>0.5709,0.1704,0.3049,0.0082</t>
-  </si>
-  <si>
-    <t>0.2006,0.0612,0.8144,0.0031</t>
-  </si>
-  <si>
-    <t>0.5487,0.0797,0.4934,0.0058</t>
-  </si>
-  <si>
-    <t>0.1374,0.0420,0.8951,0.0018</t>
-  </si>
-  <si>
-    <t>0.5071,0.0681,0.5372,0.0060</t>
-  </si>
-  <si>
-    <t>0.4041,0.3083,0.3216,0.0100</t>
-  </si>
-  <si>
-    <t>0.4360,0.2778,0.3197,0.0099</t>
-  </si>
-  <si>
-    <t>0.4168,0.2565,0.3700,0.0098</t>
-  </si>
-  <si>
-    <t>0.3713,0.3347,0.2943,0.0073</t>
-  </si>
-  <si>
-    <t>0.3773,0.2515,0.3671,0.0048</t>
-  </si>
-  <si>
-    <t>0.4104,0.2410,0.3413,0.0049</t>
-  </si>
-  <si>
-    <t>0.6071,0.1520,0.2805,0.0088</t>
-  </si>
-  <si>
-    <t>0.5379,0.1783,0.3134,0.0074</t>
-  </si>
-  <si>
-    <t>0.3185,0.6784,0.0855,0.0167</t>
-  </si>
-  <si>
-    <t>0.3972,0.5983,0.0848,0.0101</t>
-  </si>
-  <si>
-    <t>0.2997,0.6782,0.1158,0.0172</t>
-  </si>
-  <si>
-    <t>0.4693,0.5256,0.1144,0.0161</t>
-  </si>
-  <si>
-    <t>0.5302,0.4550,0.1035,0.0156</t>
-  </si>
-  <si>
-    <t>0.4971,0.2194,0.3444,0.0105</t>
-  </si>
-  <si>
-    <t>0.6562,0.1090,0.3007,0.0069</t>
-  </si>
-  <si>
-    <t>0.6376,0.1564,0.2965,0.0159</t>
-  </si>
-  <si>
-    <t>0.4788,0.2327,0.3257,0.0111</t>
-  </si>
-  <si>
-    <t>0.6523,0.1776,0.2222,0.0134</t>
-  </si>
-  <si>
-    <t>0.0889,0.0821,0.8758,0.0016</t>
-  </si>
-  <si>
-    <t>0.7128,0.0436,0.3431,0.0034</t>
-  </si>
-  <si>
-    <t>0.6481,0.0499,0.4230,0.0020</t>
-  </si>
-  <si>
-    <t>0.5772,0.0509,0.4758,0.0021</t>
-  </si>
-  <si>
-    <t>0.4096,0.1750,0.3420,0.0028</t>
-  </si>
-  <si>
-    <t>0.5435,0.4123,0.1432,0.0330</t>
-  </si>
-  <si>
-    <t>0.3615,0.6163,0.0919,0.0107</t>
-  </si>
-  <si>
-    <t>0.3162,0.6537,0.1092,0.0143</t>
-  </si>
-  <si>
-    <t>0.3385,0.6671,0.0829,0.0139</t>
-  </si>
-  <si>
-    <t>0.3085,0.6625,0.1189,0.0153</t>
-  </si>
-  <si>
-    <t>0.5203,0.4453,0.1266,0.0227</t>
-  </si>
-  <si>
-    <t>0.5562,0.4022,0.1151,0.0198</t>
-  </si>
-  <si>
-    <t>0.4630,0.4657,0.1592,0.0170</t>
-  </si>
-  <si>
-    <t>0.3705,0.3047,0.3561,0.0105</t>
-  </si>
-  <si>
-    <t>0.4485,0.4201,0.1920,0.0111</t>
-  </si>
-  <si>
-    <t>0.5801,0.3582,0.1500,0.0185</t>
-  </si>
-  <si>
-    <t>0.3253,0.0518,0.7221,0.0034</t>
-  </si>
-  <si>
-    <t>0.2601,0.0468,0.7879,0.0028</t>
-  </si>
-  <si>
-    <t>0.5428,0.0380,0.5963,0.0046</t>
-  </si>
-  <si>
-    <t>0.0250,0.0669,0.9699,0.0012</t>
-  </si>
-  <si>
-    <t>0.5767,0.0702,0.4846,0.0043</t>
-  </si>
-  <si>
-    <t>0.0057,0.1223,0.9870,0.0005</t>
-  </si>
-  <si>
-    <t>0.4923,0.0425,0.6258,0.0028</t>
-  </si>
-  <si>
-    <t>0.7180,0.1082,0.2106,0.0062</t>
-  </si>
-  <si>
-    <t>0.5205,0.2055,0.3289,0.0126</t>
-  </si>
-  <si>
-    <t>0.6135,0.0825,0.3593,0.0048</t>
-  </si>
-  <si>
-    <t>0.6065,0.1043,0.3473,0.0050</t>
-  </si>
-  <si>
-    <t>0.4988,0.5106,0.0761,0.0135</t>
-  </si>
-  <si>
-    <t>0.4427,0.5441,0.1020,0.0138</t>
-  </si>
-  <si>
-    <t>0.4332,0.5830,0.0833,0.0110</t>
-  </si>
-  <si>
-    <t>0.6543,0.3274,0.0969,0.0158</t>
-  </si>
-  <si>
-    <t>0.4345,0.5713,0.0883,0.0236</t>
-  </si>
-  <si>
-    <t>0.4578,0.5568,0.0800,0.0188</t>
-  </si>
-  <si>
-    <t>0.4691,0.5273,0.0916,0.0162</t>
-  </si>
-  <si>
-    <t>0.5150,0.5115,0.0764,0.0297</t>
-  </si>
-  <si>
-    <t>0.3261,0.2717,0.3878,0.0055</t>
-  </si>
-  <si>
-    <t>0.0427,0.0749,0.9365,0.0011</t>
-  </si>
-  <si>
-    <t>0.1564,0.0728,0.8630,0.0028</t>
-  </si>
-  <si>
-    <t>0.6252,0.0443,0.4596,0.0042</t>
-  </si>
-  <si>
-    <t>0.5956,0.0181,0.5788,0.0026</t>
-  </si>
-  <si>
-    <t>0.5257,0.1400,0.4304,0.0089</t>
-  </si>
-  <si>
-    <t>0.6823,0.0919,0.2995,0.0057</t>
-  </si>
-  <si>
-    <t>0.4767,0.0814,0.4870,0.0038</t>
-  </si>
-  <si>
-    <t>0.6591,0.2130,0.1500,0.0091</t>
-  </si>
-  <si>
-    <t>0.5359,0.3140,0.2435,0.0219</t>
-  </si>
-  <si>
-    <t>0.7612,0.0838,0.2186,0.0139</t>
-  </si>
-  <si>
-    <t>0.4535,0.4225,0.2382,0.0298</t>
-  </si>
-  <si>
-    <t>0.7293,0.1809,0.1391,0.0190</t>
-  </si>
-  <si>
-    <t>0.4139,0.4217,0.1922,0.0098</t>
+    <t>0.9374,0.0177,0.0079,0.0191</t>
+  </si>
+  <si>
+    <t>0.0636,0.0255,0.0039,0.9562</t>
+  </si>
+  <si>
+    <t>0.8475,0.1492,0.0129,0.0159</t>
+  </si>
+  <si>
+    <t>0.3853,0.0137,0.0076,0.7203</t>
+  </si>
+  <si>
+    <t>0.9892,0.0085,0.0024,0.0016</t>
+  </si>
+  <si>
+    <t>0.9832,0.0157,0.0023,0.0026</t>
+  </si>
+  <si>
+    <t>0.9841,0.0082,0.0045,0.0035</t>
+  </si>
+  <si>
+    <t>0.9885,0.0077,0.0035,0.0016</t>
+  </si>
+  <si>
+    <t>0.9888,0.0065,0.0030,0.0024</t>
+  </si>
+  <si>
+    <t>0.9825,0.0127,0.0051,0.0025</t>
+  </si>
+  <si>
+    <t>0.9809,0.0177,0.0048,0.0022</t>
+  </si>
+  <si>
+    <t>0.9865,0.0074,0.0053,0.0019</t>
+  </si>
+  <si>
+    <t>0.8837,0.0406,0.0763,0.0027</t>
+  </si>
+  <si>
+    <t>0.6996,0.0257,0.4141,0.0048</t>
+  </si>
+  <si>
+    <t>0.3842,0.0691,0.6441,0.0036</t>
+  </si>
+  <si>
+    <t>0.0364,0.0251,0.9681,0.0020</t>
+  </si>
+  <si>
+    <t>0.6476,0.1034,0.2892,0.0127</t>
+  </si>
+  <si>
+    <t>0.0665,0.9458,0.0084,0.0013</t>
+  </si>
+  <si>
+    <t>0.0513,0.9505,0.0221,0.0017</t>
+  </si>
+  <si>
+    <t>0.3726,0.6614,0.0388,0.0027</t>
+  </si>
+  <si>
+    <t>0.0415,0.9617,0.0106,0.0008</t>
+  </si>
+  <si>
+    <t>0.0070,0.9912,0.0049,0.0005</t>
+  </si>
+  <si>
+    <t>0.5128,0.0263,0.6379,0.0038</t>
+  </si>
+  <si>
+    <t>0.6231,0.0199,0.4781,0.0173</t>
+  </si>
+  <si>
+    <t>0.0025,0.0100,0.9961,0.0006</t>
+  </si>
+  <si>
+    <t>0.4953,0.0245,0.6442,0.0035</t>
+  </si>
+  <si>
+    <t>0.0216,0.0419,0.9727,0.0019</t>
+  </si>
+  <si>
+    <t>0.2544,0.0117,0.8679,0.0033</t>
+  </si>
+  <si>
+    <t>0.0004,0.0050,0.9986,0.0005</t>
+  </si>
+  <si>
+    <t>0.3459,0.7659,0.0138,0.0038</t>
+  </si>
+  <si>
+    <t>0.6119,0.3426,0.0790,0.0055</t>
+  </si>
+  <si>
+    <t>0.0008,0.0697,0.9970,0.0006</t>
+  </si>
+  <si>
+    <t>0.0704,0.7799,0.1739,0.0022</t>
+  </si>
+  <si>
+    <t>0.7503,0.2599,0.0495,0.0166</t>
+  </si>
+  <si>
+    <t>0.6759,0.2486,0.1178,0.0106</t>
+  </si>
+  <si>
+    <t>0.8960,0.1617,0.0114,0.0016</t>
+  </si>
+  <si>
+    <t>0.0919,0.8810,0.0776,0.0039</t>
+  </si>
+  <si>
+    <t>0.0221,0.9109,0.2037,0.0086</t>
+  </si>
+  <si>
+    <t>0.1073,0.1103,0.8558,0.0100</t>
+  </si>
+  <si>
+    <t>0.1860,0.0635,0.8251,0.0053</t>
+  </si>
+  <si>
+    <t>0.0777,0.0177,0.9347,0.0068</t>
+  </si>
+  <si>
+    <t>0.0265,0.3098,0.9152,0.0044</t>
+  </si>
+  <si>
+    <t>0.0067,0.9836,0.0530,0.0017</t>
+  </si>
+  <si>
+    <t>0.0600,0.0965,0.9104,0.0030</t>
+  </si>
+  <si>
+    <t>0.5818,0.4235,0.0309,0.0451</t>
+  </si>
+  <si>
+    <t>0.0149,0.9800,0.0073,0.0031</t>
+  </si>
+  <si>
+    <t>0.0063,0.9846,0.0205,0.0041</t>
+  </si>
+  <si>
+    <t>0.0138,0.9766,0.0288,0.0018</t>
+  </si>
+  <si>
+    <t>0.0021,0.7643,0.9665,0.0009</t>
+  </si>
+  <si>
+    <t>0.0018,0.3618,0.9881,0.0005</t>
+  </si>
+  <si>
+    <t>0.0809,0.0478,0.9120,0.0074</t>
+  </si>
+  <si>
+    <t>0.0199,0.0263,0.9822,0.0010</t>
+  </si>
+  <si>
+    <t>0.0027,0.0682,0.9922,0.0006</t>
+  </si>
+  <si>
+    <t>0.0075,0.2527,0.9654,0.0012</t>
+  </si>
+  <si>
+    <t>0.9464,0.0490,0.0261,0.0011</t>
+  </si>
+  <si>
+    <t>0.9280,0.0608,0.0260,0.0056</t>
+  </si>
+  <si>
+    <t>0.9375,0.0832,0.0095,0.0039</t>
+  </si>
+  <si>
+    <t>0.0409,0.4347,0.8143,0.0046</t>
+  </si>
+  <si>
+    <t>0.9715,0.0265,0.0105,0.0013</t>
+  </si>
+  <si>
+    <t>0.9899,0.0063,0.0031,0.0014</t>
+  </si>
+  <si>
+    <t>0.9715,0.0195,0.0150,0.0024</t>
+  </si>
+  <si>
+    <t>0.0023,0.9785,0.5762,0.0018</t>
+  </si>
+  <si>
+    <t>0.0076,0.2779,0.9689,0.0021</t>
+  </si>
+  <si>
+    <t>0.0208,0.3124,0.9157,0.0042</t>
+  </si>
+  <si>
+    <t>0.0023,0.9629,0.7820,0.0011</t>
+  </si>
+  <si>
+    <t>0.0016,0.0636,0.9943,0.0006</t>
+  </si>
+  <si>
+    <t>0.0220,0.9687,0.0158,0.0012</t>
+  </si>
+  <si>
+    <t>0.0009,0.9985,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.7461,0.0603,0.2496,0.0104</t>
+  </si>
+  <si>
+    <t>0.5369,0.3967,0.1093,0.0131</t>
+  </si>
+  <si>
+    <t>0.0022,0.5389,0.9807,0.0010</t>
+  </si>
+  <si>
+    <t>0.0049,0.9140,0.7461,0.0015</t>
+  </si>
+  <si>
+    <t>0.0092,0.9138,0.6729,0.0026</t>
+  </si>
+  <si>
+    <t>0.0013,0.9965,0.0336,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.9794,0.5606,0.0007</t>
+  </si>
+  <si>
+    <t>0.0978,0.0101,0.0488,0.8900</t>
+  </si>
+  <si>
+    <t>0.0128,0.0175,0.0057,0.9880</t>
+  </si>
+  <si>
+    <t>0.0141,0.0139,0.0033,0.9887</t>
+  </si>
+  <si>
+    <t>0.0231,0.0486,0.0067,0.9770</t>
+  </si>
+  <si>
+    <t>0.0314,0.0115,0.0083,0.9756</t>
+  </si>
+  <si>
+    <t>0.0441,0.0250,0.0083,0.9657</t>
+  </si>
+  <si>
+    <t>0.0048,0.9599,0.5835,0.0014</t>
+  </si>
+  <si>
+    <t>0.0031,0.8102,0.9409,0.0011</t>
+  </si>
+  <si>
+    <t>0.0127,0.8561,0.6926,0.0044</t>
+  </si>
+  <si>
+    <t>0.0314,0.5852,0.7984,0.0060</t>
+  </si>
+  <si>
+    <t>0.0040,0.9860,0.1318,0.0005</t>
+  </si>
+  <si>
+    <t>0.0104,0.9255,0.4371,0.0041</t>
+  </si>
+  <si>
+    <t>0.9858,0.0120,0.0037,0.0015</t>
+  </si>
+  <si>
+    <t>0.9867,0.0090,0.0042,0.0018</t>
+  </si>
+  <si>
+    <t>0.9846,0.0136,0.0031,0.0023</t>
+  </si>
+  <si>
+    <t>0.9778,0.0165,0.0062,0.0034</t>
+  </si>
+  <si>
+    <t>0.9859,0.0126,0.0040,0.0019</t>
+  </si>
+  <si>
+    <t>0.9857,0.0104,0.0031,0.0019</t>
+  </si>
+  <si>
+    <t>0.9831,0.0125,0.0055,0.0022</t>
+  </si>
+  <si>
+    <t>0.9725,0.0306,0.0086,0.0012</t>
+  </si>
+  <si>
+    <t>0.9910,0.0045,0.0016,0.0020</t>
+  </si>
+  <si>
+    <t>0.9741,0.0213,0.0068,0.0042</t>
+  </si>
+  <si>
+    <t>0.9909,0.0053,0.0022,0.0019</t>
+  </si>
+  <si>
+    <t>0.9917,0.0043,0.0038,0.0013</t>
+  </si>
+  <si>
+    <t>0.9887,0.0065,0.0033,0.0020</t>
+  </si>
+  <si>
+    <t>0.9825,0.0151,0.0059,0.0016</t>
+  </si>
+  <si>
+    <t>0.9831,0.0135,0.0069,0.0014</t>
+  </si>
+  <si>
+    <t>0.9887,0.0069,0.0027,0.0021</t>
+  </si>
+  <si>
+    <t>0.0006,0.0221,0.9980,0.0005</t>
+  </si>
+  <si>
+    <t>0.0782,0.0236,0.8910,0.0365</t>
+  </si>
+  <si>
+    <t>0.7658,0.1942,0.0422,0.0120</t>
+  </si>
+  <si>
+    <t>0.2447,0.0475,0.7994,0.0089</t>
+  </si>
+  <si>
+    <t>0.0574,0.9493,0.0138,0.0017</t>
+  </si>
+  <si>
+    <t>0.0187,0.9793,0.0102,0.0007</t>
+  </si>
+  <si>
+    <t>0.5870,0.5808,0.0148,0.0018</t>
+  </si>
+  <si>
+    <t>0.4144,0.7210,0.0166,0.0024</t>
+  </si>
+  <si>
+    <t>0.0559,0.9397,0.0244,0.0012</t>
+  </si>
+  <si>
+    <t>0.0085,0.9893,0.0057,0.0005</t>
+  </si>
+  <si>
+    <t>0.7199,0.3754,0.0209,0.0017</t>
+  </si>
+  <si>
+    <t>0.7973,0.1175,0.1114,0.0100</t>
+  </si>
+  <si>
+    <t>0.2858,0.0293,0.7974,0.0072</t>
+  </si>
+  <si>
+    <t>0.7046,0.2189,0.1224,0.0147</t>
+  </si>
+  <si>
+    <t>0.8446,0.0384,0.1355,0.0041</t>
+  </si>
+  <si>
+    <t>0.5354,0.3583,0.2137,0.0510</t>
+  </si>
+  <si>
+    <t>0.0025,0.9940,0.0074,0.0012</t>
+  </si>
+  <si>
+    <t>0.0030,0.9936,0.0088,0.0007</t>
+  </si>
+  <si>
+    <t>0.0194,0.9711,0.0145,0.0034</t>
+  </si>
+  <si>
+    <t>0.0012,0.9966,0.0164,0.0005</t>
+  </si>
+  <si>
+    <t>0.2550,0.7980,0.0229,0.0020</t>
+  </si>
+  <si>
+    <t>0.9328,0.0923,0.0122,0.0011</t>
+  </si>
+  <si>
+    <t>0.8773,0.1795,0.0126,0.0036</t>
+  </si>
+  <si>
+    <t>0.9107,0.0837,0.0272,0.0045</t>
+  </si>
+  <si>
+    <t>0.9769,0.0160,0.0088,0.0026</t>
+  </si>
+  <si>
+    <t>0.9757,0.0219,0.0045,0.0028</t>
+  </si>
+  <si>
+    <t>0.9375,0.0934,0.0059,0.0037</t>
+  </si>
+  <si>
+    <t>0.9827,0.0092,0.0072,0.0045</t>
+  </si>
+  <si>
+    <t>0.9434,0.0359,0.0415,0.0045</t>
+  </si>
+  <si>
+    <t>0.9678,0.0222,0.0135,0.0048</t>
+  </si>
+  <si>
+    <t>0.9734,0.0170,0.0094,0.0054</t>
+  </si>
+  <si>
+    <t>0.0149,0.7224,0.8008,0.0030</t>
+  </si>
+  <si>
+    <t>0.0036,0.5764,0.9574,0.0008</t>
+  </si>
+  <si>
+    <t>0.0238,0.5807,0.8077,0.0064</t>
+  </si>
+  <si>
+    <t>0.1510,0.0963,0.8116,0.0026</t>
+  </si>
+  <si>
+    <t>0.8807,0.0477,0.0875,0.0084</t>
+  </si>
+  <si>
+    <t>0.7910,0.2089,0.0322,0.0114</t>
+  </si>
+  <si>
+    <t>0.4282,0.0327,0.6931,0.0095</t>
+  </si>
+  <si>
+    <t>0.5982,0.4036,0.0407,0.0038</t>
+  </si>
+  <si>
+    <t>0.4169,0.0142,0.0059,0.6903</t>
+  </si>
+  <si>
+    <t>0.0025,0.0042,0.0046,0.9958</t>
+  </si>
+  <si>
+    <t>0.0236,0.0404,0.0142,0.9721</t>
+  </si>
+  <si>
+    <t>0.0453,0.0192,0.0205,0.9586</t>
+  </si>
+  <si>
+    <t>0.0032,0.9771,0.4050,0.0025</t>
+  </si>
+  <si>
+    <t>0.9766,0.0128,0.0124,0.0030</t>
+  </si>
+  <si>
+    <t>0.6565,0.3306,0.0597,0.0051</t>
+  </si>
+  <si>
+    <t>0.9745,0.0174,0.0102,0.0036</t>
+  </si>
+  <si>
+    <t>0.7994,0.1656,0.0571,0.0043</t>
+  </si>
+  <si>
+    <t>0.9413,0.0335,0.0108,0.0089</t>
+  </si>
+  <si>
+    <t>0.8227,0.0750,0.0225,0.0686</t>
+  </si>
+  <si>
+    <t>0.9651,0.0083,0.0127,0.0138</t>
+  </si>
+  <si>
+    <t>0.0052,0.4832,0.9672,0.0048</t>
+  </si>
+  <si>
+    <t>0.8800,0.0565,0.0185,0.0462</t>
+  </si>
+  <si>
+    <t>0.9590,0.0254,0.0148,0.0071</t>
+  </si>
+  <si>
+    <t>0.2281,0.8198,0.0213,0.0054</t>
+  </si>
+  <si>
+    <t>0.7575,0.3088,0.0194,0.0076</t>
+  </si>
+  <si>
+    <t>0.8422,0.1472,0.0613,0.0087</t>
+  </si>
+  <si>
+    <t>0.1633,0.8587,0.0219,0.0123</t>
+  </si>
+  <si>
+    <t>0.6311,0.3750,0.0444,0.0052</t>
+  </si>
+  <si>
+    <t>0.7250,0.2501,0.0560,0.0032</t>
+  </si>
+  <si>
+    <t>0.9810,0.0125,0.0057,0.0028</t>
+  </si>
+  <si>
+    <t>0.9781,0.0142,0.0091,0.0028</t>
+  </si>
+  <si>
+    <t>0.9853,0.0105,0.0040,0.0024</t>
+  </si>
+  <si>
+    <t>0.9679,0.0183,0.0104,0.0073</t>
+  </si>
+  <si>
+    <t>0.9778,0.0144,0.0099,0.0028</t>
+  </si>
+  <si>
+    <t>0.9492,0.0314,0.0301,0.0062</t>
+  </si>
+  <si>
+    <t>0.9820,0.0104,0.0072,0.0031</t>
+  </si>
+  <si>
+    <t>0.9800,0.0172,0.0045,0.0024</t>
+  </si>
+  <si>
+    <t>0.7497,0.3079,0.0303,0.0041</t>
+  </si>
+  <si>
+    <t>0.8560,0.2015,0.0136,0.0021</t>
+  </si>
+  <si>
+    <t>0.3663,0.6662,0.0331,0.0030</t>
+  </si>
+  <si>
+    <t>0.7187,0.2353,0.1008,0.0074</t>
+  </si>
+  <si>
+    <t>0.9442,0.0728,0.0081,0.0048</t>
+  </si>
+  <si>
+    <t>0.9308,0.0502,0.0279,0.0076</t>
+  </si>
+  <si>
+    <t>0.9848,0.0088,0.0038,0.0032</t>
+  </si>
+  <si>
+    <t>0.9645,0.0264,0.0186,0.0045</t>
+  </si>
+  <si>
+    <t>0.0007,0.1027,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.8818,0.0966,0.0514,0.0028</t>
+  </si>
+  <si>
+    <t>0.0033,0.0316,0.9911,0.0019</t>
+  </si>
+  <si>
+    <t>0.0085,0.1523,0.9775,0.0016</t>
+  </si>
+  <si>
+    <t>0.0386,0.0253,0.9650,0.0036</t>
+  </si>
+  <si>
+    <t>0.0010,0.7179,0.9863,0.0005</t>
+  </si>
+  <si>
+    <t>0.0021,0.1866,0.9909,0.0005</t>
+  </si>
+  <si>
+    <t>0.0049,0.0080,0.9944,0.0007</t>
+  </si>
+  <si>
+    <t>0.0115,0.0631,0.9807,0.0015</t>
+  </si>
+  <si>
+    <t>0.2766,0.0467,0.7843,0.0032</t>
+  </si>
+  <si>
+    <t>0.6004,0.1425,0.3295,0.0199</t>
+  </si>
+  <si>
+    <t>0.6034,0.3553,0.0981,0.0199</t>
+  </si>
+  <si>
+    <t>0.4884,0.1519,0.2919,0.0043</t>
+  </si>
+  <si>
+    <t>0.4614,0.2693,0.2075,0.0084</t>
+  </si>
+  <si>
+    <t>0.4071,0.2230,0.3313,0.0104</t>
+  </si>
+  <si>
+    <t>0.7005,0.1175,0.2155,0.0075</t>
+  </si>
+  <si>
+    <t>0.5801,0.1790,0.2469,0.0062</t>
+  </si>
+  <si>
+    <t>0.6515,0.4960,0.0182,0.0040</t>
+  </si>
+  <si>
+    <t>0.7117,0.3844,0.0236,0.0031</t>
+  </si>
+  <si>
+    <t>0.9349,0.0840,0.0121,0.0022</t>
+  </si>
+  <si>
+    <t>0.9621,0.0414,0.0111,0.0046</t>
+  </si>
+  <si>
+    <t>0.7981,0.2704,0.0259,0.0032</t>
+  </si>
+  <si>
+    <t>0.5444,0.3934,0.0851,0.0105</t>
+  </si>
+  <si>
+    <t>0.9183,0.0335,0.0449,0.0032</t>
+  </si>
+  <si>
+    <t>0.8665,0.0738,0.0566,0.0112</t>
+  </si>
+  <si>
+    <t>0.5811,0.1069,0.4257,0.0373</t>
+  </si>
+  <si>
+    <t>0.8107,0.0292,0.2001,0.0042</t>
+  </si>
+  <si>
+    <t>0.0028,0.0347,0.9928,0.0016</t>
+  </si>
+  <si>
+    <t>0.0325,0.2377,0.9090,0.0063</t>
+  </si>
+  <si>
+    <t>0.3084,0.0817,0.7281,0.0166</t>
+  </si>
+  <si>
+    <t>0.0975,0.1783,0.8295,0.0047</t>
+  </si>
+  <si>
+    <t>0.0581,0.4399,0.6878,0.0113</t>
+  </si>
+  <si>
+    <t>0.9803,0.0151,0.0039,0.0041</t>
+  </si>
+  <si>
+    <t>0.9802,0.0150,0.0056,0.0021</t>
+  </si>
+  <si>
+    <t>0.9681,0.0250,0.0179,0.0029</t>
+  </si>
+  <si>
+    <t>0.9829,0.0108,0.0068,0.0020</t>
+  </si>
+  <si>
+    <t>0.9793,0.0174,0.0040,0.0026</t>
+  </si>
+  <si>
+    <t>0.9703,0.0298,0.0086,0.0033</t>
+  </si>
+  <si>
+    <t>0.9763,0.0170,0.0083,0.0029</t>
+  </si>
+  <si>
+    <t>0.9783,0.0178,0.0051,0.0029</t>
+  </si>
+  <si>
+    <t>0.0374,0.1170,0.9283,0.0013</t>
+  </si>
+  <si>
+    <t>0.2036,0.7850,0.0629,0.0051</t>
+  </si>
+  <si>
+    <t>0.8213,0.0502,0.1615,0.0167</t>
+  </si>
+  <si>
+    <t>0.0049,0.0235,0.9942,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.0401,0.9968,0.0005</t>
+  </si>
+  <si>
+    <t>0.0472,0.1963,0.9044,0.0045</t>
+  </si>
+  <si>
+    <t>0.0008,0.1050,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0761,0.1530,0.8440,0.0031</t>
+  </si>
+  <si>
+    <t>0.0005,0.0349,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.0085,0.0423,0.9866,0.0010</t>
+  </si>
+  <si>
+    <t>0.0965,0.0320,0.9278,0.0029</t>
+  </si>
+  <si>
+    <t>0.8054,0.0266,0.2625,0.0075</t>
+  </si>
+  <si>
+    <t>0.5776,0.0380,0.4313,0.0383</t>
+  </si>
+  <si>
+    <t>0.8922,0.0635,0.0449,0.0054</t>
+  </si>
+  <si>
+    <t>0.9492,0.0644,0.0114,0.0023</t>
+  </si>
+  <si>
+    <t>0.9856,0.0108,0.0040,0.0015</t>
+  </si>
+  <si>
+    <t>0.9707,0.0377,0.0058,0.0026</t>
+  </si>
+  <si>
+    <t>0.9800,0.0162,0.0083,0.0019</t>
+  </si>
+  <si>
+    <t>0.9805,0.0139,0.0070,0.0027</t>
+  </si>
+  <si>
+    <t>0.9811,0.0163,0.0057,0.0018</t>
+  </si>
+  <si>
+    <t>0.9829,0.0116,0.0067,0.0025</t>
+  </si>
+  <si>
+    <t>0.9898,0.0073,0.0023,0.0017</t>
+  </si>
+  <si>
+    <t>0.0409,0.0952,0.9227,0.0015</t>
+  </si>
+  <si>
+    <t>0.0029,0.1250,0.9863,0.0005</t>
+  </si>
+  <si>
+    <t>0.0331,0.1372,0.9281,0.0020</t>
+  </si>
+  <si>
+    <t>0.1470,0.0618,0.8559,0.0098</t>
+  </si>
+  <si>
+    <t>0.0240,0.0287,0.9684,0.0039</t>
+  </si>
+  <si>
+    <t>0.1812,0.1315,0.7711,0.0450</t>
+  </si>
+  <si>
+    <t>0.2195,0.0651,0.8014,0.0080</t>
+  </si>
+  <si>
+    <t>0.0660,0.0657,0.9069,0.0060</t>
+  </si>
+  <si>
+    <t>0.9243,0.0245,0.0112,0.0283</t>
+  </si>
+  <si>
+    <t>0.0328,0.0344,0.0090,0.9676</t>
+  </si>
+  <si>
+    <t>0.1648,0.0073,0.0026,0.9239</t>
+  </si>
+  <si>
+    <t>0.0098,0.0038,0.0058,0.9907</t>
+  </si>
+  <si>
+    <t>0.0056,0.0220,0.0040,0.9929</t>
+  </si>
+  <si>
+    <t>0.8752,0.0968,0.0235,0.0132</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2037,7 +2037,7 @@
         <v>259</v>
       </c>
       <c r="C8" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D8" t="s">
         <v>270</v>
@@ -2051,7 +2051,7 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D9" t="s">
         <v>271</v>
@@ -2065,7 +2065,7 @@
         <v>259</v>
       </c>
       <c r="C10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D10" t="s">
         <v>272</v>
@@ -2079,7 +2079,7 @@
         <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D11" t="s">
         <v>273</v>
@@ -2093,7 +2093,7 @@
         <v>259</v>
       </c>
       <c r="C12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D12" t="s">
         <v>274</v>
@@ -2107,7 +2107,7 @@
         <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D13" t="s">
         <v>275</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2261,7 +2261,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
         <v>286</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2709,7 +2709,7 @@
         <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D56" t="s">
         <v>318</v>
@@ -2723,7 +2723,7 @@
         <v>259</v>
       </c>
       <c r="C57" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D57" t="s">
         <v>319</v>
@@ -2737,7 +2737,7 @@
         <v>259</v>
       </c>
       <c r="C58" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D58" t="s">
         <v>320</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2779,7 +2779,7 @@
         <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D61" t="s">
         <v>323</v>
@@ -2793,7 +2793,7 @@
         <v>259</v>
       </c>
       <c r="C62" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D62" t="s">
         <v>324</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3171,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="C89" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D89" t="s">
         <v>351</v>
@@ -3185,7 +3185,7 @@
         <v>259</v>
       </c>
       <c r="C90" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D90" t="s">
         <v>352</v>
@@ -3199,7 +3199,7 @@
         <v>259</v>
       </c>
       <c r="C91" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D91" t="s">
         <v>353</v>
@@ -3213,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="C92" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D92" t="s">
         <v>354</v>
@@ -3255,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D95" t="s">
         <v>357</v>
@@ -3269,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D96" t="s">
         <v>358</v>
@@ -3283,7 +3283,7 @@
         <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D97" t="s">
         <v>359</v>
@@ -3297,7 +3297,7 @@
         <v>259</v>
       </c>
       <c r="C98" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D98" t="s">
         <v>360</v>
@@ -3325,7 +3325,7 @@
         <v>259</v>
       </c>
       <c r="C100" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D100" t="s">
         <v>362</v>
@@ -3339,7 +3339,7 @@
         <v>259</v>
       </c>
       <c r="C101" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D101" t="s">
         <v>363</v>
@@ -3353,7 +3353,7 @@
         <v>259</v>
       </c>
       <c r="C102" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D102" t="s">
         <v>364</v>
@@ -3367,7 +3367,7 @@
         <v>259</v>
       </c>
       <c r="C103" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D103" t="s">
         <v>365</v>
@@ -3381,7 +3381,7 @@
         <v>259</v>
       </c>
       <c r="C104" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D104" t="s">
         <v>366</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3759,7 +3759,7 @@
         <v>259</v>
       </c>
       <c r="C131" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D131" t="s">
         <v>393</v>
@@ -3773,7 +3773,7 @@
         <v>259</v>
       </c>
       <c r="C132" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D132" t="s">
         <v>394</v>
@@ -3801,7 +3801,7 @@
         <v>259</v>
       </c>
       <c r="C134" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D134" t="s">
         <v>396</v>
@@ -3815,7 +3815,7 @@
         <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D135" t="s">
         <v>397</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -4011,7 +4011,7 @@
         <v>259</v>
       </c>
       <c r="C149" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D149" t="s">
         <v>411</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4039,7 +4039,7 @@
         <v>259</v>
       </c>
       <c r="C151" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D151" t="s">
         <v>413</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4137,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D158" t="s">
         <v>420</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4207,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
         <v>425</v>
@@ -4249,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="C166" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D166" t="s">
         <v>428</v>
@@ -4263,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="C167" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D167" t="s">
         <v>429</v>
@@ -4277,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="C168" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D168" t="s">
         <v>430</v>
@@ -4305,7 +4305,7 @@
         <v>259</v>
       </c>
       <c r="C170" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D170" t="s">
         <v>432</v>
@@ -4319,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="C171" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D171" t="s">
         <v>433</v>
@@ -4333,7 +4333,7 @@
         <v>259</v>
       </c>
       <c r="C172" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D172" t="s">
         <v>434</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4403,7 +4403,7 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
         <v>439</v>
@@ -4431,7 +4431,7 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D179" t="s">
         <v>441</v>
@@ -4445,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
         <v>442</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4739,7 +4739,7 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
         <v>463</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -4921,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="C214" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D214" t="s">
         <v>476</v>
@@ -4935,7 +4935,7 @@
         <v>259</v>
       </c>
       <c r="C215" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D215" t="s">
         <v>477</v>
@@ -4949,7 +4949,7 @@
         <v>259</v>
       </c>
       <c r="C216" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D216" t="s">
         <v>478</v>
@@ -4963,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="C217" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D217" t="s">
         <v>479</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5215,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="C235" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D235" t="s">
         <v>497</v>
@@ -5229,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D236" t="s">
         <v>498</v>
@@ -5243,7 +5243,7 @@
         <v>259</v>
       </c>
       <c r="C237" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D237" t="s">
         <v>499</v>
@@ -5271,7 +5271,7 @@
         <v>259</v>
       </c>
       <c r="C239" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D239" t="s">
         <v>501</v>
@@ -5285,7 +5285,7 @@
         <v>259</v>
       </c>
       <c r="C240" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D240" t="s">
         <v>502</v>
@@ -5299,7 +5299,7 @@
         <v>259</v>
       </c>
       <c r="C241" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D241" t="s">
         <v>503</v>
@@ -5313,7 +5313,7 @@
         <v>259</v>
       </c>
       <c r="C242" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D242" t="s">
         <v>504</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
